--- a/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
@@ -15,8 +15,10 @@
     <sheet name="Schedule OS - FY2025-26" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="FTC - Withholding Tax" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Capital Gains FY2025-26" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CG Summary by Symbol" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notes for CA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Capital Gains FY2024-25" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FIFO Lots Register" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="CG Summary by Symbol" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Notes for CA" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1024,7 +1026,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1216,7 +1218,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1266,7 +1268,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1416,7 +1418,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1516,7 +1518,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1566,7 +1568,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1666,7 +1668,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2016,7 +2018,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2066,7 +2068,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2166,7 +2168,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2266,14 +2268,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>97332</v>
+        <v>114327</v>
       </c>
       <c r="I39" t="n">
-        <v>102211</v>
+        <v>120056</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2416,7 +2418,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2566,7 +2568,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2616,7 +2618,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2666,7 +2668,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2766,7 +2768,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2866,7 +2868,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3158,7 +3160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3308,7 +3310,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3408,7 +3410,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3558,7 +3560,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3608,7 +3610,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -3658,7 +3660,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -3708,7 +3710,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3985,10 +3987,10 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>10744668</v>
+        <v>10761663</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13132538</v>
+        <v>13150383</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>6044042</v>
@@ -4014,7 +4016,2814 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FIFO lot register rebuilt from inception statement (actual acquisition dates &amp; IBKR cost basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Acquisition Date</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Cost (local)</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AIQ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1446.7626</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1045.0003</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4328.7104</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1242.1005</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BLBD</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2588.8043</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BTI</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1162.7674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1808.2609</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1004.5002</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E11" t="n">
+        <v>610.9003</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E12" t="n">
+        <v>532.0005</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E13" t="n">
+        <v>493.0002</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1375.8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IGPT</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1587.9724</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4837.0003</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E17" t="n">
+        <v>737.2001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MCHI</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1527.1769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2455.0003</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2226.8242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>R6C0d</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>42</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1279.38</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E22" t="n">
+        <v>541.0005</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SAUS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E23" t="n">
+        <v>286.7052</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E24" t="n">
+        <v>916.0003</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6571.3043</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>45632</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3762.7976</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (CY2025 open)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E27" t="n">
+        <v>968.8003</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4568.T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E28" t="n">
+        <v>372297.6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AIQ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>36</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1446.7626</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="E30" t="n">
+        <v>142.7341</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1045.0003</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4328.7104</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1242.1005</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BTI</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1162.7674</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1808.2609</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1004.5002</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E37" t="n">
+        <v>610.9003</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E38" t="n">
+        <v>532.0005</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>45685</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1590.5203</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E40" t="n">
+        <v>493.0002</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1375.8</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IGPT</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>33</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1587.9724</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4837.0003</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E44" t="n">
+        <v>737.2001</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MCHI</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>27</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1527.1769</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2455.0003</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2226.8242</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NOVd</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>45737</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2103</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="E49" t="n">
+        <v>504.0742</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>R6C0d</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1279.38</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E51" t="n">
+        <v>541.0005</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SAUS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E52" t="n">
+        <v>286.7052</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E53" t="n">
+        <v>916.0003</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>60</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6571.3043</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="E55" t="n">
+        <v>968.8003</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>31-Mar-2025 (FY2025-26 open)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>VKTX</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>33</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>45685</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1114.4215</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>STCG INR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LTCG INR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Gain/(Loss) INR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Proceeds USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-24754</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-24754</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1033.06</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1323.36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-11927</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-11927</v>
+      </c>
+      <c r="E3" t="n">
+        <v>943.76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1098.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-5042</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-5042</v>
+      </c>
+      <c r="E4" t="n">
+        <v>625.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>689.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-37169</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-37169</v>
+      </c>
+      <c r="E5" t="n">
+        <v>976.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1377.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4568.T</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-62984</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-62984</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1813.33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2376.26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9984.T</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-79014</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-79014</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2414.58</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3020.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AIRd</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>51913</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51913</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2119.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1615.78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4318</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4318</v>
+      </c>
+      <c r="E9" t="n">
+        <v>194.64</v>
+      </c>
+      <c r="F9" t="n">
+        <v>142.73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31127</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31127</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1392.12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8543</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8543</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4338.54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4328.71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>117514</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>117514</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2600.64</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1242.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>70904</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>70904</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2930.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2095.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BTI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>50815</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50815</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1736.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1162.77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>34263</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34263</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2154.36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1788.57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BYDDY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>57588</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>57588</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4199.58</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3521.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>102511</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>102511</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3856.14</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2667.26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CLPT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-64103</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-64103</v>
+      </c>
+      <c r="E18" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1160.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-36559</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-36559</v>
+      </c>
+      <c r="E19" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1409.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CRCL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-223568</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-223568</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6992.41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9612.389999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-100182</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-100182</v>
+      </c>
+      <c r="E21" t="n">
+        <v>908.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2066.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10781</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10781</v>
+      </c>
+      <c r="E22" t="n">
+        <v>726.12</v>
+      </c>
+      <c r="F22" t="n">
+        <v>609.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4568</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4568</v>
+      </c>
+      <c r="E23" t="n">
+        <v>576.67</v>
+      </c>
+      <c r="F23" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>25954</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25954</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1898.37</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1590.52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>27449</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>27449</v>
+      </c>
+      <c r="E25" t="n">
+        <v>807.28</v>
+      </c>
+      <c r="F25" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2410</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2410</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1339.02</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1339.02</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IGPT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7951</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7951</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1664.68</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1587.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>62760</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>62760</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F28" t="n">
+        <v>693.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7709</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7709</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4847.88</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>21707</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>21707</v>
+      </c>
+      <c r="E30" t="n">
+        <v>979.42</v>
+      </c>
+      <c r="F30" t="n">
+        <v>737.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MCHI</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8782</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8782</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1599.08</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1527.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>57223</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>57223</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3076.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>36216</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>36216</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3772.76</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3388.18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NOVd</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-133380</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-133380</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3707.59</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5558.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>99889</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>99889</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2811.59</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1636.31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-50070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-50070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>980</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1555.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>R6C0d</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9756</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9756</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1512.26</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1502.76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-39033</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-39033</v>
+      </c>
+      <c r="E38" t="n">
+        <v>975.12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1460.11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3655</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3655</v>
+      </c>
+      <c r="E39" t="n">
+        <v>574.78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>102843</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>102843</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4676.7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3467.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SIEd</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>119874</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>119874</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5311.54</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4183.69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-6403</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-6403</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1421.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1549.24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>32092</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>32092</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2948.4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2798.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-14731</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-14731</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1997.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2185.47</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>42090</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>42090</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1446.18</v>
+      </c>
+      <c r="F45" t="n">
+        <v>968.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VKTX</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>490</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>490</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1122.49</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1114.42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WCBR</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>-21356</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-21356</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1857.22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2210.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4079,240 +6888,312 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Schedule FA period</t>
+          <t>Account funded</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calendar Year 2025 (01-Jan-2025 to 31-Dec-2025) — for ITR AY 2026-27</t>
+          <t>First deposit 2024-09-06 (inception statement)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Income / CG period</t>
+          <t>Schedule FA period</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FY 2025-26 (01-Apr-2025 to 31-Mar-2026)</t>
+          <t>Calendar Year 2025 (01-Jan-2025 to 31-Dec-2025) — for ITR AY 2026-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Source data</t>
+          <t>Income / CG period</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IBKR Activity Statement Annual (CY2025) + Fiscal (FY2025-26)</t>
+          <t>FY 2025-26 (01-Apr-2025 to 31-Mar-2026); also FY 2024-25 sheet for prior year</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Starting NAV CY2025</t>
+          <t>Source data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USD 58,595.36</t>
+          <t>IBKR Activity Statements: Inception FY2024-25 + Annual CY2025 + Fiscal FY2025-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ending NAV CY2025</t>
+          <t>FIFO method</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USD 88,426.07</t>
+          <t>Actual buy dates &amp; IBKR Basis from inception replay; splits (LRCX 10:1, NFLX 10:1) applied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deposits CY2025</t>
+          <t>Starting NAV CY2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USD 20,150.00</t>
+          <t>USD 58,595.36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dividends CY2025</t>
+          <t>Ending NAV CY2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USD 1,157.41 / INR 100,191 (Rule 115)</t>
+          <t>USD 88,426.07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Interest CY2025</t>
+          <t>Deposits CY2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USD 167.80 / INR 14,620 (Rule 115)</t>
+          <t>USD 20,150.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dividends FY2025-26</t>
+          <t>Deposits since inception (to 31-Mar-2025)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USD 1,211.95 / INR 105,546</t>
+          <t>USD 69,730.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Interest FY2025-26</t>
+          <t>Dividends CY2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USD 165.81 / INR 14,519</t>
+          <t>USD 1,157.41 / INR 100,191 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STCG (INR)</t>
+          <t>Interest CY2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>238,154</t>
+          <t>USD 167.80 / INR 14,620 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LTCG (INR)</t>
+          <t>Dividends FY2025-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>USD 1,211.95 / INR 105,546</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A1 Foreign Bank/Depository</t>
+          <t>Interest FY2025-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
+          <t>USD 165.81 / INR 14,519</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A2 Custodial Account</t>
+          <t>STCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Applicable — see sheet</t>
+          <t>303,420</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A3 Equity &amp; Debt Interest</t>
+          <t>LTCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Applicable — 69 securities lines (held at any time in CY2025)</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ADR country practice</t>
+          <t>STCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
+          <t>-138,990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CPNG</t>
+          <t>LTCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NFLX split</t>
+          <t>A1 Foreign Bank/Depository</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10-for-1 split on 14/17-Nov-2025 reflected in IBKR; FIFO uses post-split quantities from statement</t>
+          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HYU</t>
+          <t>A2 Custodial Account</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+          <t>Applicable — see sheet; opening date 06-Sep-2024 (first funding)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>A3 Equity &amp; Debt Interest</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Applicable — 69 securities lines (held at any time in CY2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ADR country practice</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NFLX split</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LRCX split</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Action required</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1) Replace placeholder acquisition dates for pre-2025 lots using prior IBKR statements; 2) Confirm exact SBI TT Buy card rates; 3) Obtain PortfolioAnalyst for true peak NAV; 4) Map withholding to Schedule FSI/TR under applicable DTAA; 5) Confirm account opening date.</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1) Confirm exact SBI TT Buy card rates; 2) Obtain PortfolioAnalyst for true peak NAV; 3) Map withholding to Schedule FSI/TR under DTAA.</t>
         </is>
       </c>
     </row>
@@ -4337,7 +7218,7 @@
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -4903,7 +7784,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -5107,7 +7988,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -5158,7 +8039,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -5209,7 +8090,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -5311,7 +8192,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -5413,7 +8294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -5464,7 +8345,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -5566,7 +8447,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -5923,7 +8804,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5974,7 +8855,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -6076,7 +8957,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -6178,14 +9059,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1142.4</v>
+        <v>1341.86</v>
       </c>
       <c r="J36" t="n">
-        <v>1142.4</v>
+        <v>1341.86</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -6331,7 +9212,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -6484,7 +9365,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -6535,7 +9416,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -6586,7 +9467,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -6688,7 +9569,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -6790,7 +9671,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -7096,7 +9977,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -7249,7 +10130,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -7351,7 +10232,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -7504,7 +10385,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -7555,7 +10436,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -7606,7 +10487,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -7657,7 +10538,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Prior to 01-Jan-2025 (confirm)</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -7938,10 +10819,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>124672.99</v>
+        <v>124872.45</v>
       </c>
       <c r="J71" t="n">
-        <v>146781.39</v>
+        <v>146980.85</v>
       </c>
       <c r="K71" t="n">
         <v>67553.8</v>
@@ -8186,7 +11067,7 @@
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8274,7 +11155,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prior to / during 2024 (confirm from account opening docs)</t>
+          <t>2024-09-06 (first funding per IBKR deposits)</t>
         </is>
       </c>
     </row>
@@ -15895,10 +18776,10 @@
         <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>85.2</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -15927,10 +18808,10 @@
         <v>-1.19</v>
       </c>
       <c r="G11" t="n">
-        <v>85.2</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="12">
@@ -15959,10 +18840,10 @@
         <v>1.34</v>
       </c>
       <c r="G12" t="n">
-        <v>85.2</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -15991,10 +18872,10 @@
         <v>2.85</v>
       </c>
       <c r="G13" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -16023,10 +18904,10 @@
         <v>6.02</v>
       </c>
       <c r="G14" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15">
@@ -16055,10 +18936,10 @@
         <v>-6.01</v>
       </c>
       <c r="G15" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-512</v>
+        <v>-506</v>
       </c>
     </row>
     <row r="16">
@@ -16087,10 +18968,10 @@
         <v>2.41</v>
       </c>
       <c r="G16" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
@@ -16119,10 +19000,10 @@
         <v>4.33</v>
       </c>
       <c r="G17" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18">
@@ -16151,10 +19032,10 @@
         <v>-4.32</v>
       </c>
       <c r="G18" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-368</v>
+        <v>-364</v>
       </c>
     </row>
     <row r="19">
@@ -21960,7 +24841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -22148,13 +25029,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F4" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -22174,7 +25055,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M4" t="n">
         <v>118469</v>
@@ -22183,16 +25064,12 @@
         <v>85</v>
       </c>
       <c r="O4" t="n">
-        <v>89034</v>
+        <v>87258</v>
       </c>
       <c r="P4" t="n">
-        <v>29350</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>31127</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22209,13 +25086,13 @@
         <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45474</v>
+        <v>45587</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F5" t="n">
-        <v>388</v>
+        <v>275</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -22235,7 +25112,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M5" t="n">
         <v>369210</v>
@@ -22244,16 +25121,12 @@
         <v>85</v>
       </c>
       <c r="O5" t="n">
-        <v>368806</v>
+        <v>360582</v>
       </c>
       <c r="P5" t="n">
-        <v>318</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>8543</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22270,13 +25143,13 @@
         <v>9</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F6" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -22296,7 +25169,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M6" t="n">
         <v>221314</v>
@@ -22305,16 +25178,12 @@
         <v>85</v>
       </c>
       <c r="O6" t="n">
-        <v>105827</v>
+        <v>103715</v>
       </c>
       <c r="P6" t="n">
-        <v>115402</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>117514</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22388,13 +25257,13 @@
         <v>33</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>45474</v>
+        <v>45569</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F8" t="n">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -22414,7 +25283,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M8" t="n">
         <v>147759</v>
@@ -22423,16 +25292,12 @@
         <v>86</v>
       </c>
       <c r="O8" t="n">
-        <v>99068</v>
+        <v>96859</v>
       </c>
       <c r="P8" t="n">
-        <v>48605</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>50815</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22449,13 +25314,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45474</v>
+        <v>45569</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F9" t="n">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -22475,7 +25340,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M9" t="n">
         <v>183336</v>
@@ -22484,16 +25349,12 @@
         <v>85</v>
       </c>
       <c r="O9" t="n">
-        <v>152386</v>
+        <v>148988</v>
       </c>
       <c r="P9" t="n">
-        <v>30865</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>34263</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22567,13 +25428,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F11" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -22593,7 +25454,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M11" t="n">
         <v>109386</v>
@@ -22602,16 +25463,12 @@
         <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>75750</v>
+        <v>74239</v>
       </c>
       <c r="P11" t="n">
-        <v>33607</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>35119</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22685,13 +25542,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F13" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -22711,7 +25568,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M13" t="n">
         <v>61793</v>
@@ -22720,16 +25577,12 @@
         <v>85</v>
       </c>
       <c r="O13" t="n">
-        <v>51963</v>
+        <v>50927</v>
       </c>
       <c r="P13" t="n">
-        <v>9744</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>10781</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22746,13 +25599,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F14" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -22772,7 +25625,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M14" t="n">
         <v>49075</v>
@@ -22781,16 +25634,12 @@
         <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>45326</v>
+        <v>44422</v>
       </c>
       <c r="P14" t="n">
-        <v>3663</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>4568</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22864,13 +25713,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F16" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -22890,7 +25739,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M16" t="n">
         <v>68700</v>
@@ -22899,16 +25748,12 @@
         <v>85</v>
       </c>
       <c r="O16" t="n">
-        <v>42004</v>
+        <v>41166</v>
       </c>
       <c r="P16" t="n">
-        <v>26611</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>27449</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22925,13 +25770,13 @@
         <v>33</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>45474</v>
+        <v>45638</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F17" t="n">
-        <v>388</v>
+        <v>224</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -22951,7 +25796,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>141665</v>
@@ -22960,16 +25805,12 @@
         <v>86</v>
       </c>
       <c r="O17" t="n">
-        <v>135295</v>
+        <v>133628</v>
       </c>
       <c r="P17" t="n">
-        <v>6284</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>7951</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22986,13 +25827,13 @@
         <v>6</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>45474</v>
+        <v>45600</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F18" t="n">
-        <v>388</v>
+        <v>262</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -23012,7 +25853,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>85.2</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>412555</v>
@@ -23021,16 +25862,12 @@
         <v>85</v>
       </c>
       <c r="O18" t="n">
-        <v>412112</v>
+        <v>404760</v>
       </c>
       <c r="P18" t="n">
-        <v>357</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>7709</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23047,13 +25884,13 @@
         <v>27</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>45474</v>
+        <v>45569</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F19" t="n">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -23073,7 +25910,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M19" t="n">
         <v>136081</v>
@@ -23082,16 +25919,12 @@
         <v>86</v>
       </c>
       <c r="O19" t="n">
-        <v>130115</v>
+        <v>127214</v>
       </c>
       <c r="P19" t="n">
-        <v>5880</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>8782</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23108,13 +25941,13 @@
         <v>10</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F20" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -23134,7 +25967,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M20" t="n">
         <v>83349</v>
@@ -23143,14 +25976,14 @@
         <v>85</v>
       </c>
       <c r="O20" t="n">
-        <v>62809</v>
+        <v>61556</v>
       </c>
       <c r="P20" t="n">
-        <v>20454</v>
+        <v>21707</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
+          <t>LRCX 10-for-1 split on 02/03-Oct-2024 reflected in FIFO qty</t>
         </is>
       </c>
     </row>
@@ -23169,13 +26002,13 @@
         <v>6</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>45474</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F21" t="n">
-        <v>388</v>
+        <v>266</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -23195,7 +26028,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M21" t="n">
         <v>261810</v>
@@ -23204,16 +26037,12 @@
         <v>85</v>
       </c>
       <c r="O21" t="n">
-        <v>209166</v>
+        <v>204502</v>
       </c>
       <c r="P21" t="n">
-        <v>52559</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>57223</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -23230,13 +26059,13 @@
         <v>2.4</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>45474</v>
+        <v>45638</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F22" t="n">
-        <v>388</v>
+        <v>224</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -23256,7 +26085,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>85.2</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>238090</v>
@@ -23265,16 +26094,12 @@
         <v>85</v>
       </c>
       <c r="O22" t="n">
-        <v>189725</v>
+        <v>187387</v>
       </c>
       <c r="P22" t="n">
-        <v>48279</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>50617</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -23405,13 +26230,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F25" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -23431,7 +26256,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M25" t="n">
         <v>48914</v>
@@ -23440,16 +26265,12 @@
         <v>85</v>
       </c>
       <c r="O25" t="n">
-        <v>46093</v>
+        <v>45174</v>
       </c>
       <c r="P25" t="n">
-        <v>2736</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>3655</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -23523,13 +26344,13 @@
         <v>6</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="F27" t="n">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -23549,7 +26370,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M27" t="n">
         <v>123070</v>
@@ -23558,16 +26379,12 @@
         <v>85</v>
       </c>
       <c r="O27" t="n">
-        <v>82542</v>
+        <v>80895</v>
       </c>
       <c r="P27" t="n">
-        <v>40443</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>42090</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -23698,13 +26515,13 @@
         <v>42</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>45474</v>
+        <v>45545</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>45863</v>
       </c>
       <c r="F30" t="n">
-        <v>389</v>
+        <v>318</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -23724,7 +26541,7 @@
         <v>98.92</v>
       </c>
       <c r="L30" t="n">
-        <v>88.5</v>
+        <v>91.72</v>
       </c>
       <c r="M30" t="n">
         <v>127357</v>
@@ -23733,16 +26550,12 @@
         <v>255</v>
       </c>
       <c r="O30" t="n">
-        <v>113225</v>
+        <v>117345</v>
       </c>
       <c r="P30" t="n">
-        <v>13876</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>9756</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -23816,13 +26629,13 @@
         <v>24</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>45474</v>
+        <v>45587</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="F32" t="n">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -23833,7 +26646,7 @@
         <v>1339.02</v>
       </c>
       <c r="I32" t="n">
-        <v>1585.36</v>
+        <v>1339.02</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -23842,7 +26655,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="M32" t="n">
         <v>113950</v>
@@ -23851,14 +26664,14 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>135073</v>
+        <v>111540</v>
       </c>
       <c r="P32" t="n">
-        <v>-21122</v>
+        <v>2410</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
+          <t>Cash merger / redemption — cost from IBKR realized P/L</t>
         </is>
       </c>
     </row>
@@ -24333,13 +27146,13 @@
         <v>6</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>45474</v>
+        <v>45544</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>46077</v>
       </c>
       <c r="F41" t="n">
-        <v>603</v>
+        <v>533</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -24359,7 +27172,7 @@
         <v>91.34999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="M41" t="n">
         <v>62155</v>
@@ -24368,16 +27181,12 @@
         <v>21</v>
       </c>
       <c r="O41" t="n">
-        <v>55031</v>
+        <v>53933</v>
       </c>
       <c r="P41" t="n">
-        <v>7103</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Opening lot — confirm acquisition date from prior IBKR statements</t>
-        </is>
-      </c>
+        <v>8201</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -25356,7 +28165,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>238154</v>
+        <v>303420</v>
       </c>
     </row>
     <row r="61">
@@ -25376,7 +28185,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>238154</v>
+        <v>303420</v>
       </c>
     </row>
     <row r="63"/>
@@ -25390,7 +28199,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Opening lots acquired before 01-Jan-2025 use placeholder acquisition date 01-Jul-2024 for holding-period tests — replace with actual trade dates from prior-year IBKR statements before finalising LTCG/STCG.</t>
+          <t>FIFO from inception trades (FY2024-25 statement). Holding period uses actual buy dates. Account funded from Sep-2024 — no lot reaches 24 months by 31-Mar-2026, so all FY2025-26 gains are STCG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cost = IBKR trade Basis allocated FIFO; sale consideration = IBKR Proceeds; sell commission deducted. INR via Rule 115 (TT Buy on last day of month preceding event).</t>
         </is>
       </c>
     </row>
@@ -25405,1059 +28221,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capital gains on foreign shares/ETFs — FY 2024-25 (AY 2025-26). FIFO from inception (account funded Sep-2024). All holdings &lt;24 months → STCG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>STCG INR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LTCG INR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Gain/(Loss) INR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sale Proceeds USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>-24754</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-24754</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1033.06</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1323.36</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>CCY</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Acquisition Date</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Sale Date</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Sale Proceeds (USD)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Cost (USD)</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Comm (USD)</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Sale FX (Rule115)</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Cost FX (Rule115)</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Sale (INR)</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Comm (INR)</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Cost (INR)</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Gain/(Loss) INR</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3069</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-11927</v>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-11927</v>
-      </c>
-      <c r="E3" t="n">
-        <v>943.76</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>45632</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>45726</v>
       </c>
       <c r="F3" t="n">
-        <v>1098.62</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>STCG</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2465.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3762.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>214358</v>
+      </c>
+      <c r="N3" t="n">
+        <v>93</v>
+      </c>
+      <c r="O3" t="n">
+        <v>316639</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-102375</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3416</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-5042</v>
+          <t>BLBD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="C4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>45587</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>45726</v>
+      </c>
+      <c r="F4" t="n">
+        <v>139</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>STCG</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2060.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2588.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>179126</v>
+      </c>
+      <c r="N4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O4" t="n">
+        <v>215647</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-36615</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TOTAL STCG (INR)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>-138990</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOTAL LTCG (INR)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>-5042</v>
-      </c>
-      <c r="E4" t="n">
-        <v>625.75</v>
-      </c>
-      <c r="F4" t="n">
-        <v>689.24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-37169</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-37169</v>
-      </c>
-      <c r="E5" t="n">
-        <v>976.52</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1377.32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4568.T</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-62984</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-62984</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1813.33</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2376.26</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>9984.T</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-79014</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-79014</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2414.58</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3020.79</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AIRd</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>51913</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>51913</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2119.92</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1615.78</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4318</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4318</v>
-      </c>
-      <c r="E9" t="n">
-        <v>194.64</v>
-      </c>
-      <c r="F9" t="n">
-        <v>142.73</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>29350</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>29350</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1392.12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>318</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>318</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4338.54</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4328.71</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>115402</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>115402</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2600.64</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1242.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>70904</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>70904</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2930.1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2095.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BTI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>48605</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48605</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1736.3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1162.77</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BX</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>30865</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30865</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2154.36</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1788.57</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BYDDY</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>57588</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>57588</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4199.58</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3521.86</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>100999</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>100999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3856.14</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2667.26</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CLPT</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-64103</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-64103</v>
-      </c>
-      <c r="E18" t="n">
-        <v>425.04</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1160.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CPNG</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-36559</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-36559</v>
-      </c>
-      <c r="E19" t="n">
-        <v>953.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1409.25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CRCL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>-223568</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-223568</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6992.41</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9612.389999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DUOL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-100182</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-100182</v>
-      </c>
-      <c r="E21" t="n">
-        <v>908.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2066.04</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>9744</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9744</v>
-      </c>
-      <c r="E22" t="n">
-        <v>726.12</v>
-      </c>
-      <c r="F22" t="n">
-        <v>609.9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>EMXC</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3663</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3663</v>
-      </c>
-      <c r="E23" t="n">
-        <v>576.67</v>
-      </c>
-      <c r="F23" t="n">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>25954</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>25954</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1898.37</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1590.52</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>26611</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>26611</v>
-      </c>
-      <c r="E25" t="n">
-        <v>807.28</v>
-      </c>
-      <c r="F25" t="n">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>HYU</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-21122</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-21122</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1339.02</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1585.36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>IGPT</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>6284</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>6284</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1664.68</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1587.97</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>62760</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>62760</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F28" t="n">
-        <v>693.87</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>357</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>357</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4847.88</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4837</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>20454</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>20454</v>
-      </c>
-      <c r="E30" t="n">
-        <v>979.42</v>
-      </c>
-      <c r="F30" t="n">
-        <v>737.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MCHI</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5880</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1599.08</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1527.18</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>52559</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>52559</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3076.5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2455</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>33878</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>33878</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3772.76</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3388.18</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NOVd</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>-133380</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-133380</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3707.59</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5558.5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>99889</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>99889</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2811.59</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1636.31</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ORCL</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>-50070</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-50070</v>
-      </c>
-      <c r="E36" t="n">
-        <v>980</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1555.5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>R6C0d</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>13876</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>13876</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1512.26</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1502.76</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-39033</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-39033</v>
-      </c>
-      <c r="E38" t="n">
-        <v>975.12</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1460.11</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2736</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2736</v>
-      </c>
-      <c r="E39" t="n">
-        <v>574.78</v>
-      </c>
-      <c r="F39" t="n">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>RTX</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>102843</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>102843</v>
-      </c>
-      <c r="E40" t="n">
-        <v>4676.7</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3467.2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SIEd</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>119874</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>119874</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5311.54</v>
-      </c>
-      <c r="F41" t="n">
-        <v>4183.69</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-6403</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-6403</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1421.2</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1549.24</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>30994</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>30994</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2948.4</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2798.9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>-14731</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-14731</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1997.5</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2185.47</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>40443</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>40443</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1446.18</v>
-      </c>
-      <c r="F45" t="n">
-        <v>968.8</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>VKTX</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>490</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>490</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1122.49</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1114.42</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>WCBR</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>-21356</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-21356</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1857.22</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2210.31</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TOTAL CG (INR)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>-138990</v>
       </c>
     </row>
   </sheetData>

--- a/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
@@ -4168,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4188,11 +4188,6 @@
           <t>Assessee</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ray G Stephanos</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4202,7 +4197,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U15124027 — Interactive Brokers LLC (Advisor Client; Advisor: Financial Hospital Advisory LLP)</t>
+          <t>None — Interactive Brokers LLC (Advisor Client; Advisor: None)</t>
         </is>
       </c>
     </row>
@@ -4212,11 +4207,6 @@
           <t>Customer type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4224,11 +4214,6 @@
           <t>Base currency</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4293,139 +4278,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Starting NAV CY2025</t>
+          <t>CG reconciliation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USD 58,595.36</t>
+          <t>Sheets 'Capital Gains FY2025-26' / 'FY2024-25' are formula-driven — yellow cells editable; Gain = Sale INR − Comm INR − Cost INR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ending NAV CY2025</t>
+          <t>FX Lookup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USD 88,426.07</t>
+          <t>Editable SBI TT USD/INR &amp; EUR/INR month-end rates + FCY→USD cross rates</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deposits CY2025</t>
+          <t>Starting NAV CY2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USD 20,150.00</t>
+          <t>USD 58,595.36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deposits since inception (to 31-Mar-2025)</t>
+          <t>Ending NAV CY2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USD 69,730.01</t>
+          <t>USD 88,426.07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dividends CY2025</t>
+          <t>Deposits CY2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USD 1,157.41 / INR 100,191 (Rule 115)</t>
+          <t>USD 20,150.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Interest CY2025</t>
+          <t>Deposits since inception (to 31-Mar-2025)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USD 167.80 / INR 14,620 (Rule 115)</t>
+          <t>USD 69,730.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dividends FY2025-26</t>
+          <t>Dividends CY2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USD 1,211.95 / INR 105,546</t>
+          <t>USD 1,157.41 / INR 100,191 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Interest FY2025-26</t>
+          <t>Interest CY2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USD 165.81 / INR 14,519</t>
+          <t>USD 167.80 / INR 14,620 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STCG FY2025-26 (INR)</t>
+          <t>Dividends FY2025-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>303,420</t>
+          <t>USD 1,211.95 / INR 105,546</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LTCG FY2025-26 (INR)</t>
+          <t>Interest FY2025-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>USD 165.81 / INR 14,519</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STCG FY2024-25 (INR)</t>
+          <t>STCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-138,990</t>
+          <t>303,420</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LTCG FY2024-25 (INR)</t>
+          <t>LTCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4437,106 +4422,142 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A1 Foreign Bank/Depository</t>
+          <t>STCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
+          <t>-138,990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A2 Custodial Account</t>
+          <t>LTCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Applicable — see sheet; opening date 06-Sep-2024 (first funding)</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A3 Equity &amp; Debt Interest</t>
+          <t>A1 Foreign Bank/Depository</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Applicable — 69 securities lines (held at any time in CY2025)</t>
+          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADR country practice</t>
+          <t>A2 Custodial Account</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
+          <t>Applicable — see sheet; opening date 06-Sep-2024 (first funding)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CPNG</t>
+          <t>A3 Equity &amp; Debt Interest</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
+          <t>Applicable — 82 FIFO lot lines (one row per acquisition lot; sold lots match Capital Gains)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NFLX split</t>
+          <t>A3 vs CG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
+          <t>Sold lots: A3 Initial = CG Cost (INR), A3 Sale = CG Sale (INR), same Rule 115/EUR FX. Multiple buys (e.g. NOVd 21-Mar &amp; 21-Aug) appear as separate A3 rows.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LRCX split</t>
+          <t>ADR country practice</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
+          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HYU</t>
+          <t>CPNG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>NFLX split</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LRCX split</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Action required</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>1) Confirm exact SBI TT Buy card rates; 2) Obtain PortfolioAnalyst for true peak NAV; 3) Map withholding to Schedule FSI/TR under DTAA.</t>
         </is>
@@ -4553,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4689,7 +4710,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xiaomi Corp - Class B  [Ticker: 1810]  Qty: 0</t>
+          <t>Xiaomi Corp - Class B  [Ticker: 1810]  Qty: 200</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5207,7 +5228,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Airbus SE  [Ticker: AIRd]  Qty: 0</t>
+          <t>Airbus SE  [Ticker: AIRd]  Qty: 10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5231,7 +5252,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>137503</v>
+        <v>126363</v>
       </c>
       <c r="I16" t="n">
         <v>189669</v>
@@ -5243,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>180405</v>
+        <v>178531</v>
       </c>
     </row>
     <row r="17">
@@ -5257,7 +5278,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc  [Ticker: AMD]  Qty: 9</t>
+          <t>Advanced Micro Devices Inc  [Ticker: AMD]  Qty: 1.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5284,10 +5305,10 @@
         <v>12161</v>
       </c>
       <c r="I17" t="n">
-        <v>172448</v>
+        <v>17414</v>
       </c>
       <c r="J17" t="n">
-        <v>172448</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -5307,17 +5328,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon.com Inc  [Ticker: AMZN]  Qty: 0</t>
+          <t>Advanced Micro Devices Inc  [Ticker: AMD]  Qty: 9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>410 Terry Avenue North, Seattle, WA</t>
+          <t>2485 Augustine Drive, Santa Clara, CA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98109</t>
+          <t>95054</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5327,173 +5348,173 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>112152</v>
+        <v>129003</v>
       </c>
       <c r="I18" t="n">
-        <v>124553</v>
+        <v>172448</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>172448</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>118469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASML Holding NV - NY Registered Shares  [Ticker: ASML]  Qty: 3</t>
+          <t>Amazon.com Inc  [Ticker: AMZN]  Qty: 6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>De Run 6501, 5504 DR Veldhoven</t>
+          <t>410 Terry Avenue North, Seattle, WA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5504 DR</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>354302</v>
+        <v>87258</v>
       </c>
       <c r="I19" t="n">
-        <v>388169</v>
+        <v>124553</v>
       </c>
       <c r="J19" t="n">
-        <v>287161</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2362</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>369210</v>
+        <v>118469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Broadcom Inc  [Ticker: AVGO]  Qty: 0</t>
+          <t>ASML Holding NV - NY Registered Shares  [Ticker: ASML]  Qty: 6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3421 Hillview Avenue, Palo Alto, CA</t>
+          <t>De Run 6501, 5504 DR Veldhoven</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>94304</t>
+          <t>5504 DR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>177775</v>
+        <v>360582</v>
       </c>
       <c r="I20" t="n">
-        <v>232679</v>
+        <v>388169</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>914</v>
+        <v>2362</v>
       </c>
       <c r="L20" t="n">
-        <v>221314</v>
+        <v>369210</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bank of America Corp  [Ticker: BAC]  Qty: 0</t>
+          <t>ASML Holding NV - NY Registered Shares  [Ticker: ASML]  Qty: 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>100 North Tryon Street, Charlotte, NC</t>
+          <t>De Run 6501, 5504 DR Veldhoven</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>5504 DR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>178361</v>
+        <v>192802</v>
       </c>
       <c r="I21" t="n">
-        <v>262156</v>
+        <v>287161</v>
       </c>
       <c r="J21" t="n">
+        <v>287161</v>
+      </c>
+      <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
-        <v>1328</v>
-      </c>
       <c r="L21" t="n">
-        <v>249352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5507,17 +5528,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Bird Corp  [Ticker: BLBD]  Qty: 0</t>
+          <t>Broadcom Inc  [Ticker: AVGO]  Qty: 9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3920 Arkwright Road, Macon, GA</t>
+          <t>3421 Hillview Avenue, Palo Alto, CA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>94304</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5527,23 +5548,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>197477</v>
+        <v>103715</v>
       </c>
       <c r="I22" t="n">
-        <v>207374</v>
+        <v>232679</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="L22" t="n">
-        <v>179126</v>
+        <v>221314</v>
       </c>
     </row>
     <row r="23">
@@ -5557,93 +5578,93 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Global X Robotics &amp; Artificial Intelligence ETF  [Ticker: BOTZ]  Qty: 24</t>
+          <t>Bank of America Corp  [Ticker: BAC]  Qty: 60</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>c/o Global X Management Company LLC, 605 Third Avenue, New York, NY</t>
+          <t>100 North Tryon Street, Charlotte, NC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>68953</v>
+        <v>178361</v>
       </c>
       <c r="I23" t="n">
-        <v>77796</v>
+        <v>262156</v>
       </c>
       <c r="J23" t="n">
-        <v>77796</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1328</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>249352</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>British American Tobacco plc - Sponsored ADR  [Ticker: BTI]  Qty: 0</t>
+          <t>Blue Bird Corp  [Ticker: BLBD]  Qty: 60</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Globe House, 4 Temple Place, London</t>
+          <t>3920 Arkwright Road, Macon, GA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WC2R 2PG</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>102117</v>
+        <v>215647</v>
       </c>
       <c r="I24" t="n">
-        <v>155346</v>
+        <v>231620</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>147759</v>
+        <v>179126</v>
       </c>
     </row>
     <row r="25">
@@ -5657,67 +5678,67 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blackstone Inc  [Ticker: BX]  Qty: 0</t>
+          <t>Global X Robotics &amp; Artificial Intelligence ETF  [Ticker: BOTZ]  Qty: 24</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>345 Park Avenue, New York, NY</t>
+          <t>c/o Global X Management Company LLC, 605 Third Avenue, New York, NY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>176282</v>
+        <v>68953</v>
       </c>
       <c r="I25" t="n">
-        <v>192751</v>
+        <v>77796</v>
       </c>
       <c r="J25" t="n">
+        <v>77796</v>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>2430</v>
-      </c>
       <c r="L25" t="n">
-        <v>183336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>44</v>
+        <v>234</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BYD Co Ltd - Unsponsored ADR  [Ticker: BYDDY]  Qty: 0</t>
+          <t>British American Tobacco plc - Sponsored ADR  [Ticker: BTI]  Qty: 33</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No. 3009 BYD Road, Pingshan, Shenzhen</t>
+          <t>Globe House, 4 Temple Place, London</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>518118</t>
+          <t>WC2R 2PG</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5727,23 +5748,23 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>299710</v>
+        <v>96859</v>
       </c>
       <c r="I26" t="n">
-        <v>375736</v>
+        <v>155346</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4035</v>
+        <v>6600</v>
       </c>
       <c r="L26" t="n">
-        <v>357384</v>
+        <v>147759</v>
       </c>
     </row>
     <row r="27">
@@ -5757,17 +5778,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Caterpillar Inc  [Ticker: CAT]  Qty: 0</t>
+          <t>Blackstone Inc  [Ticker: BX]  Qty: 12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5205 N O'Connor Boulevard, Irving, TX</t>
+          <t>345 Park Avenue, New York, NY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75039</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5777,73 +5798,73 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>92721</v>
+        <v>148988</v>
       </c>
       <c r="I27" t="n">
-        <v>345009</v>
+        <v>192751</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2618</v>
+        <v>2430</v>
       </c>
       <c r="L27" t="n">
-        <v>328158</v>
+        <v>183336</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ClearPoint Neuro Inc  [Ticker: CLPT]  Qty: 42</t>
+          <t>BYD Co Ltd - Unsponsored ADR  [Ticker: BYDDY]  Qty: 42</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>120 S Sierra Avenue, Solana Beach, CA</t>
+          <t>No. 3009 BYD Road, Pingshan, Shenzhen</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92075</t>
+          <t>518118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>102504</v>
+        <v>299710</v>
       </c>
       <c r="I28" t="n">
-        <v>103803</v>
+        <v>375736</v>
       </c>
       <c r="J28" t="n">
-        <v>51406</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4035</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>357384</v>
       </c>
     </row>
     <row r="29">
@@ -5857,17 +5878,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Coupang Inc (Delaware) - Class A  [Ticker: CPNG]  Qty: 50</t>
+          <t>Caterpillar Inc  [Ticker: CAT]  Qty: 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>720 Olive Way, Suite 600, Seattle, WA</t>
+          <t>5205 N O'Connor Boulevard, Irving, TX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>75039</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5877,23 +5898,23 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>122816</v>
+        <v>74239</v>
       </c>
       <c r="I29" t="n">
-        <v>126086</v>
+        <v>115003</v>
       </c>
       <c r="J29" t="n">
-        <v>105530</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2618</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>109386</v>
       </c>
     </row>
     <row r="30">
@@ -5907,17 +5928,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 10</t>
+          <t>Caterpillar Inc  [Ticker: CAT]  Qty: 6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>99 High Street, Boston, MA</t>
+          <t>5205 N O'Connor Boulevard, Irving, TX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02110</t>
+          <t>75039</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5927,23 +5948,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>705409</v>
+        <v>151323</v>
       </c>
       <c r="I30" t="n">
-        <v>724188</v>
+        <v>230006</v>
       </c>
       <c r="J30" t="n">
-        <v>70950</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>523710</v>
+        <v>218772</v>
       </c>
     </row>
     <row r="31">
@@ -5957,17 +5978,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc  [Ticker: CSCO]  Qty: 20</t>
+          <t>ClearPoint Neuro Inc  [Ticker: CLPT]  Qty: 42</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>170 West Tasman Drive, San Jose, CA</t>
+          <t>120 S Sierra Avenue, Solana Beach, CA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>92075</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5977,20 +5998,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>118869</v>
+        <v>102504</v>
       </c>
       <c r="I31" t="n">
-        <v>137837</v>
+        <v>103803</v>
       </c>
       <c r="J31" t="n">
-        <v>137837</v>
+        <v>51406</v>
       </c>
       <c r="K31" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -5999,25 +6020,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Deutsche Bank AG - Registered Shares  [Ticker: DB]  Qty: 33</t>
+          <t>Coupang Inc (Delaware) - Class A  [Ticker: CPNG]  Qty: 50</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Taunusanlage 12, Frankfurt am Main</t>
+          <t>720 Olive Way, Suite 600, Seattle, WA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60325</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6031,13 +6052,13 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>105287</v>
+        <v>122816</v>
       </c>
       <c r="I32" t="n">
-        <v>113849</v>
+        <v>126086</v>
       </c>
       <c r="J32" t="n">
-        <v>113849</v>
+        <v>105530</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -6057,17 +6078,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Duolingo Inc  [Ticker: DUOL]  Qty: 9</t>
+          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5900 Penn Avenue, Pittsburgh, PA</t>
+          <t>99 High Street, Boston, MA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>02110</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6077,23 +6098,23 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>182535</v>
+        <v>14093</v>
       </c>
       <c r="I33" t="n">
-        <v>184849</v>
+        <v>14468</v>
       </c>
       <c r="J33" t="n">
-        <v>141318</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>10463</v>
       </c>
     </row>
     <row r="34">
@@ -6107,43 +6128,43 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WisdomTree Japan Hedged Equity Fund  [Ticker: DXJ]  Qty: 0</t>
+          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>c/o WisdomTree Investments Inc, 250 West 34th Street, New York, NY</t>
+          <t>99 High Street, Boston, MA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>02110</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>56380</v>
+        <v>267759</v>
       </c>
       <c r="I34" t="n">
-        <v>64966</v>
+        <v>274887</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>61793</v>
+        <v>198790</v>
       </c>
     </row>
     <row r="35">
@@ -6157,43 +6178,43 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Markets ex China ETF  [Ticker: EMXC]  Qty: 0</t>
+          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 30.0554</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+          <t>99 High Street, Boston, MA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>02110</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>42519</v>
+        <v>423558</v>
       </c>
       <c r="I35" t="n">
-        <v>51595</v>
+        <v>434833</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>49075</v>
+        <v>314458</v>
       </c>
     </row>
     <row r="36">
@@ -6207,17 +6228,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>General Dynamics Corp  [Ticker: GD]  Qty: 0</t>
+          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11011 Sunset Hills Road, Reston, VA</t>
+          <t>99 High Street, Boston, MA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>02110</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6227,23 +6248,23 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>135512</v>
+        <v>134133</v>
       </c>
       <c r="I36" t="n">
-        <v>169848</v>
+        <v>135833</v>
       </c>
       <c r="J36" t="n">
+        <v>70950</v>
+      </c>
+      <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>1543</v>
-      </c>
       <c r="L36" t="n">
-        <v>161552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6257,17 +6278,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GE Aerospace / General Electric  [Ticker: GE]  Qty: 0</t>
+          <t>Cisco Systems Inc  [Ticker: CSCO]  Qty: 20</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1 Neumann Way, Cincinnati, OH</t>
+          <t>170 West Tasman Drive, San Jose, CA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>95134</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6277,52 +6298,52 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>42632</v>
+        <v>118869</v>
       </c>
       <c r="I37" t="n">
-        <v>72228</v>
+        <v>137837</v>
       </c>
       <c r="J37" t="n">
+        <v>137837</v>
+      </c>
+      <c r="K37" t="n">
+        <v>724</v>
+      </c>
+      <c r="L37" t="n">
         <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>255</v>
-      </c>
-      <c r="L37" t="n">
-        <v>68700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SPDR Gold Shares (World Gold Trust)  [Ticker: GLD]  Qty: 10</t>
+          <t>Deutsche Bank AG - Registered Shares  [Ticker: DB]  Qty: 33</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>c/o World Gold Trust Services LLC, 685 Third Avenue, New York, NY</t>
+          <t>Taunusanlage 12, Frankfurt am Main</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -6331,13 +6352,13 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>268064</v>
+        <v>105287</v>
       </c>
       <c r="I38" t="n">
-        <v>354579</v>
+        <v>113849</v>
       </c>
       <c r="J38" t="n">
-        <v>354579</v>
+        <v>113849</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -6349,51 +6370,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hyundai Motor Co - Reg S GDR  [Ticker: HYU]  Qty: 0</t>
+          <t>Duolingo Inc  [Ticker: DUOL]  Qty: 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12 Heolleung-ro, Seocho-gu, Seoul</t>
+          <t>5900 Penn Avenue, Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>06797</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Global Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>114327</v>
+        <v>84914</v>
       </c>
       <c r="I39" t="n">
-        <v>120056</v>
+        <v>85990</v>
       </c>
       <c r="J39" t="n">
+        <v>47106</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>6221</v>
-      </c>
       <c r="L39" t="n">
-        <v>113950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6407,17 +6428,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>International Business Machines Corp  [Ticker: IBM]  Qty: 5</t>
+          <t>Duolingo Inc  [Ticker: DUOL]  Qty: 6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1 New Orchard Road, Armonk, NY</t>
+          <t>5900 Penn Avenue, Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6427,20 +6448,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>116974</v>
+        <v>97456</v>
       </c>
       <c r="I40" t="n">
-        <v>132510</v>
+        <v>98859</v>
       </c>
       <c r="J40" t="n">
-        <v>132510</v>
+        <v>94212</v>
       </c>
       <c r="K40" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -6457,17 +6478,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy ETF  [Ticker: ICLN]  Qty: 50</t>
+          <t>WisdomTree Japan Hedged Equity Fund  [Ticker: DXJ]  Qty: 6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+          <t>c/o WisdomTree Investments Inc, 250 West 34th Street, New York, NY</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6477,23 +6498,23 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>61898</v>
+        <v>50927</v>
       </c>
       <c r="I41" t="n">
-        <v>73500</v>
+        <v>64966</v>
       </c>
       <c r="J41" t="n">
-        <v>73500</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>61793</v>
       </c>
     </row>
     <row r="42">
@@ -6507,17 +6528,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Invesco AI and Next Gen Software ETF  [Ticker: IGPT]  Qty: 0</t>
+          <t>iShares MSCI Emerging Markets ex China ETF  [Ticker: EMXC]  Qty: 9</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>c/o Invesco Capital Management LLC, Downers Grove, IL</t>
+          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>60515</t>
+          <t>94105</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6527,23 +6548,23 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127169</v>
+        <v>44422</v>
       </c>
       <c r="I42" t="n">
-        <v>148939</v>
+        <v>51595</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>47</v>
+        <v>545</v>
       </c>
       <c r="L42" t="n">
-        <v>141665</v>
+        <v>49075</v>
       </c>
     </row>
     <row r="43">
@@ -6557,17 +6578,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Intel Corp  [Ticker: INTC]  Qty: 72</t>
+          <t>General Dynamics Corp  [Ticker: GD]  Qty: 6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2200 Mission College Boulevard, Santa Clara, CA</t>
+          <t>11011 Sunset Hills Road, Reston, VA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>95054</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6577,23 +6598,23 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>145129</v>
+        <v>135512</v>
       </c>
       <c r="I43" t="n">
-        <v>237704</v>
+        <v>169848</v>
       </c>
       <c r="J43" t="n">
-        <v>237704</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1543</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>161552</v>
       </c>
     </row>
     <row r="44">
@@ -6607,43 +6628,43 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>iShares Russell Mid-Cap ETF  [Ticker: IWR]  Qty: 10</t>
+          <t>GE Aerospace / General Electric  [Ticker: GE]  Qty: 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+          <t>1 Neumann Way, Cincinnati, OH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>82065</v>
+        <v>41166</v>
       </c>
       <c r="I44" t="n">
-        <v>86133</v>
+        <v>72228</v>
       </c>
       <c r="J44" t="n">
-        <v>86133</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>633</v>
+        <v>255</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="45">
@@ -6657,93 +6678,93 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eli Lilly &amp; Company  [Ticker: LLY]  Qty: 3.5</t>
+          <t>SPDR Gold Shares (World Gold Trust)  [Ticker: GLD]  Qty: 10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lilly Corporate Center, Indianapolis, IN</t>
+          <t>c/o World Gold Trust Services LLC, 685 Third Avenue, New York, NY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>394646</v>
+        <v>268064</v>
       </c>
       <c r="I45" t="n">
-        <v>433740</v>
+        <v>354579</v>
       </c>
       <c r="J45" t="n">
-        <v>336531</v>
+        <v>354579</v>
       </c>
       <c r="K45" t="n">
-        <v>2015</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>412555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lam Research Corp  [Ticker: LRCX]  Qty: 0</t>
+          <t>Hyundai Motor Co - Reg S GDR  [Ticker: HYU]  Qty: 24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4650 Cushing Parkway, Fremont, CA</t>
+          <t>12 Heolleung-ro, Seocho-gu, Seoul</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>94538</t>
+          <t>06797</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Global Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>61540</v>
+        <v>132061</v>
       </c>
       <c r="I46" t="n">
-        <v>87629</v>
+        <v>141842</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>587</v>
+        <v>6221</v>
       </c>
       <c r="L46" t="n">
-        <v>83349</v>
+        <v>113950</v>
       </c>
     </row>
     <row r="47">
@@ -6757,43 +6778,43 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>iShares MSCI China ETF  [Ticker: MCHI]  Qty: 0</t>
+          <t>International Business Machines Corp  [Ticker: IBM]  Qty: 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+          <t>1 New Orchard Road, Armonk, NY</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>107797</v>
+        <v>116974</v>
       </c>
       <c r="I47" t="n">
-        <v>143069</v>
+        <v>132510</v>
       </c>
       <c r="J47" t="n">
+        <v>132510</v>
+      </c>
+      <c r="K47" t="n">
+        <v>747</v>
+      </c>
+      <c r="L47" t="n">
         <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1231</v>
-      </c>
-      <c r="L47" t="n">
-        <v>136081</v>
       </c>
     </row>
     <row r="48">
@@ -6807,40 +6828,40 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc - Class A  [Ticker: META]  Qty: 2</t>
+          <t>iShares Global Clean Energy ETF  [Ticker: ICLN]  Qty: 50</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1 Meta Way, Menlo Park, CA</t>
+          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>94025</t>
+          <t>94105</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>116226</v>
+        <v>61898</v>
       </c>
       <c r="I48" t="n">
-        <v>118117</v>
+        <v>73500</v>
       </c>
       <c r="J48" t="n">
-        <v>118117</v>
+        <v>73500</v>
       </c>
       <c r="K48" t="n">
-        <v>93</v>
+        <v>570</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6857,67 +6878,67 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Microsoft Corp  [Ticker: MSFT]  Qty: 0</t>
+          <t>Invesco AI and Next Gen Software ETF  [Ticker: IGPT]  Qty: 33</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>One Microsoft Way, Redmond, WA</t>
+          <t>c/o Invesco Capital Management LLC, Downers Grove, IL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>98052</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>215471</v>
+        <v>133628</v>
       </c>
       <c r="I49" t="n">
-        <v>275254</v>
+        <v>148939</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>857</v>
+        <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>261810</v>
+        <v>141665</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nebius Group NV  [Ticker: NBIS]  Qty: 15</t>
+          <t>Intel Corp  [Ticker: INTC]  Qty: 72</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Schiphol Boulevard 165, 1118 BG Schiphol</t>
+          <t>2200 Mission College Boulevard, Santa Clara, CA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1118 BG</t>
+          <t>95054</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6931,13 +6952,13 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>87503</v>
+        <v>145129</v>
       </c>
       <c r="I50" t="n">
-        <v>112337</v>
+        <v>237704</v>
       </c>
       <c r="J50" t="n">
-        <v>112337</v>
+        <v>237704</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -6957,43 +6978,43 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netflix Inc  [Ticker: NFLX]  Qty: 10</t>
+          <t>iShares Russell Mid-Cap ETF  [Ticker: IWR]  Qty: 10</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>121 Albright Way, Los Gatos, CA</t>
+          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>95032</t>
+          <t>94105</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>182257</v>
+        <v>82065</v>
       </c>
       <c r="I51" t="n">
-        <v>250316</v>
+        <v>86133</v>
       </c>
       <c r="J51" t="n">
-        <v>83887</v>
+        <v>86133</v>
       </c>
       <c r="K51" t="n">
+        <v>633</v>
+      </c>
+      <c r="L51" t="n">
         <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>238090</v>
       </c>
     </row>
     <row r="52">
@@ -7007,59 +7028,67 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NOV  [Ticker: NOV]  Qty: 0</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+          <t>Eli Lilly &amp; Company  [Ticker: LLY]  Qty: 6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lilly Corporate Center, Indianapolis, IN</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>46285</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity / ETF</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>404760</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>433740</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>4714</v>
+        <v>2015</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>412555</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S - B Shares  [Ticker: NOVd]  Qty: 0</t>
+          <t>Eli Lilly &amp; Company  [Ticker: LLY]  Qty: 3.5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Novo Alle 1, 2880 Bagsvaerd</t>
+          <t>Lilly Corporate Center, Indianapolis, IN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7069,23 +7098,23 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>483312</v>
+        <v>218750</v>
       </c>
       <c r="I53" t="n">
-        <v>497319</v>
+        <v>336531</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>336531</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>327010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -7099,17 +7128,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NVIDIA Corp  [Ticker: NVDA]  Qty: 0</t>
+          <t>Lam Research Corp  [Ticker: LRCX]  Qty: 90</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2788 San Tomas Expressway, Santa Clara, CA</t>
+          <t>4650 Cushing Parkway, Fremont, CA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>95051</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7119,23 +7148,23 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>139413</v>
+        <v>553860</v>
       </c>
       <c r="I54" t="n">
-        <v>251553</v>
+        <v>581618</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>239266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -7149,17 +7178,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oracle Corp  [Ticker: ORCL]  Qty: 0</t>
+          <t>Lam Research Corp  [Ticker: LRCX]  Qty: 10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2300 Oracle Way, Austin, TX</t>
+          <t>4650 Cushing Parkway, Fremont, CA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>78741</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7169,23 +7198,23 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>136417</v>
+        <v>61556</v>
       </c>
       <c r="I55" t="n">
-        <v>139171</v>
+        <v>87629</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>221</v>
+        <v>587</v>
       </c>
       <c r="L55" t="n">
-        <v>86436</v>
+        <v>83349</v>
       </c>
     </row>
     <row r="56">
@@ -7199,17 +7228,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust Series 1  [Ticker: QQQ]  Qty: 2</t>
+          <t>iShares MSCI China ETF  [Ticker: MCHI]  Qty: 27</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>c/o Invesco Capital Management LLC, Downers Grove, IL</t>
+          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>60515</t>
+          <t>94105</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7219,47 +7248,47 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>98554</v>
+        <v>127214</v>
       </c>
       <c r="I56" t="n">
-        <v>109925</v>
+        <v>143069</v>
       </c>
       <c r="J56" t="n">
-        <v>109925</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>264</v>
+        <v>1231</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>136081</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Shell plc  [Ticker: R6C0d]  Qty: 0</t>
+          <t>Meta Platforms Inc - Class A  [Ticker: META]  Qty: 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shell Centre, 2 York Road, London</t>
+          <t>1 Meta Way, Menlo Park, CA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SE1 7NA</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7269,23 +7298,23 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>126579</v>
+        <v>116226</v>
       </c>
       <c r="I57" t="n">
-        <v>135302</v>
+        <v>118117</v>
       </c>
       <c r="J57" t="n">
+        <v>118117</v>
+      </c>
+      <c r="K57" t="n">
+        <v>93</v>
+      </c>
+      <c r="L57" t="n">
         <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>128694</v>
       </c>
     </row>
     <row r="58">
@@ -7299,17 +7328,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rubrik Inc - Class A  [Ticker: RBRK]  Qty: 17</t>
+          <t>Microsoft Corp  [Ticker: MSFT]  Qty: 6</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3495 Deer Creek Road, Palo Alto, CA</t>
+          <t>One Microsoft Way, Redmond, WA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>94304</t>
+          <t>98052</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7319,47 +7348,47 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>127249</v>
+        <v>204502</v>
       </c>
       <c r="I58" t="n">
-        <v>130636</v>
+        <v>275254</v>
       </c>
       <c r="J58" t="n">
-        <v>116325</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>261810</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc  [Ticker: REGN]  Qty: 3</t>
+          <t>Nebius Group NV  [Ticker: NBIS]  Qty: 15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>777 Old Saw Mill River Road, Tarrytown, NY</t>
+          <t>Schiphol Boulevard 165, 1118 BG Schiphol</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>1118 BG</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7369,20 +7398,20 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>158782</v>
+        <v>87503</v>
       </c>
       <c r="I59" t="n">
-        <v>207178</v>
+        <v>112336</v>
       </c>
       <c r="J59" t="n">
-        <v>207178</v>
+        <v>112336</v>
       </c>
       <c r="K59" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7391,51 +7420,51 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rio Tinto plc - Sponsored ADR  [Ticker: RIO]  Qty: 0</t>
+          <t>Netflix Inc  [Ticker: NFLX]  Qty: 2.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6 St James's Square, London</t>
+          <t>121 Albright Way, Los Gatos, CA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SW1Y 4AD</t>
+          <t>95032</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>45096</v>
+        <v>187387</v>
       </c>
       <c r="I60" t="n">
-        <v>51426</v>
+        <v>250316</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1723</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>48914</v>
+        <v>238090</v>
       </c>
     </row>
     <row r="61">
@@ -7449,17 +7478,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RTX Corp  [Ticker: RTX]  Qty: 0</t>
+          <t>Netflix Inc  [Ticker: NFLX]  Qty: 10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1000 Wilson Boulevard, Arlington, VA</t>
+          <t>121 Albright Way, Los Gatos, CA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>95032</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7469,70 +7498,62 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>295059</v>
+        <v>102606</v>
       </c>
       <c r="I61" t="n">
-        <v>418424</v>
+        <v>103907</v>
       </c>
       <c r="J61" t="n">
+        <v>83887</v>
+      </c>
+      <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
-        <v>1736</v>
-      </c>
       <c r="L61" t="n">
-        <v>397987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>iShares MSCI Australia UCITS ETF  [Ticker: SAUS]  Qty: 6</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>c/o BlackRock Asset Management Ireland Ltd, Dublin</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>D01 W5P4</t>
-        </is>
-      </c>
+          <t>NOV  [Ticker: NOV]  Qty: 0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity / ETF</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>28735</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>30481</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>30481</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>4714</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7541,25 +7562,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Siemens AG - Registered  [Ticker: SIEd]  Qty: 0</t>
+          <t>Novo Nordisk A/S - B Shares  [Ticker: NOVd]  Qty: 30</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Werner-von-Siemens-Strasse 1, Munich</t>
+          <t>Novo Alle 1, 2880 Bagsvaerd</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>80333</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7569,14 +7590,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>356032</v>
+        <v>149567</v>
       </c>
       <c r="I63" t="n">
-        <v>475224</v>
+        <v>175524</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7585,31 +7606,31 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>452012</v>
+        <v>112775</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Snowflake Inc  [Ticker: SNOW]  Qty: 8</t>
+          <t>Novo Nordisk A/S - B Shares  [Ticker: NOVd]  Qty: 55</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>106 East Babcock Street, Bozeman, MT</t>
+          <t>Novo Alle 1, 2880 Bagsvaerd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>59715</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7623,19 +7644,19 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>135016</v>
+        <v>303204</v>
       </c>
       <c r="I64" t="n">
-        <v>157009</v>
+        <v>321795</v>
       </c>
       <c r="J64" t="n">
-        <v>157009</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>206755</v>
       </c>
     </row>
     <row r="65">
@@ -7649,17 +7670,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Target Corp  [Ticker: TGT]  Qty: 26</t>
+          <t>NVIDIA Corp  [Ticker: NVDA]  Qty: 4.2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1000 Nicollet Mall, Minneapolis, MN</t>
+          <t>2788 San Tomas Expressway, Santa Clara, CA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>95051</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7669,23 +7690,23 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>69104</v>
+        <v>36144</v>
       </c>
       <c r="I65" t="n">
-        <v>227388</v>
+        <v>65217</v>
       </c>
       <c r="J65" t="n">
-        <v>227388</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>8298</v>
+        <v>17</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>62032</v>
       </c>
     </row>
     <row r="66">
@@ -7699,43 +7720,43 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>iShares TIPS Bond ETF  [Ticker: TIP]  Qty: 60</t>
+          <t>NVIDIA Corp  [Ticker: NVDA]  Qty: 12</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+          <t>2788 San Tomas Expressway, Santa Clara, CA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>95051</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>544684</v>
+        <v>103148</v>
       </c>
       <c r="I66" t="n">
-        <v>590019</v>
+        <v>186336</v>
       </c>
       <c r="J66" t="n">
-        <v>590019</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>19744</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>177234</v>
       </c>
     </row>
     <row r="67">
@@ -7749,17 +7770,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tesla Inc  [Ticker: TSLA]  Qty: 0</t>
+          <t>Oracle Corp  [Ticker: ORCL]  Qty: 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1 Tesla Road, Austin, TX</t>
+          <t>2300 Oracle Way, Austin, TX</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>78725</t>
+          <t>78741</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7769,97 +7790,97 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>344072</v>
+        <v>136417</v>
       </c>
       <c r="I67" t="n">
-        <v>361316</v>
+        <v>139171</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="L67" t="n">
-        <v>214358</v>
+        <v>86436</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Co - Sponsored ADR  [Ticker: TSM]  Qty: 0</t>
+          <t>Invesco QQQ Trust Series 1  [Ticker: QQQ]  Qty: 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8 Li-Hsin Road 6, Hsinchu Science Park, Hsinchu</t>
+          <t>c/o Invesco Capital Management LLC, Downers Grove, IL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>100957</v>
+        <v>98554</v>
       </c>
       <c r="I68" t="n">
-        <v>129390</v>
+        <v>109925</v>
       </c>
       <c r="J68" t="n">
+        <v>109925</v>
+      </c>
+      <c r="K68" t="n">
+        <v>264</v>
+      </c>
+      <c r="L68" t="n">
         <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1055</v>
-      </c>
-      <c r="L68" t="n">
-        <v>123070</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>234</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Viking Therapeutics Inc  [Ticker: VKTX]  Qty: 0</t>
+          <t>Shell plc  [Ticker: R6C0d]  Qty: 42</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9920 Pacific Heights Boulevard, San Diego, CA</t>
+          <t>Shell Centre, 2 York Road, London</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>92121</t>
+          <t>SE1 7NA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7869,14 +7890,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>94949</v>
+        <v>117345</v>
       </c>
       <c r="I69" t="n">
-        <v>100430</v>
+        <v>135302</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7885,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>95524</v>
+        <v>127357</v>
       </c>
     </row>
     <row r="70">
@@ -7899,22 +7920,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vanguard Total World Stock ETF  [Ticker: VT]  Qty: 9</t>
+          <t>Rubrik Inc - Class A  [Ticker: RBRK]  Qty: 17</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>c/o The Vanguard Group Inc, 100 Vanguard Boulevard, Malvern, PA</t>
+          <t>3495 Deer Creek Road, Palo Alto, CA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>94304</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7923,16 +7944,16 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>103955</v>
+        <v>127249</v>
       </c>
       <c r="I70" t="n">
-        <v>113586</v>
+        <v>130636</v>
       </c>
       <c r="J70" t="n">
-        <v>113586</v>
+        <v>116325</v>
       </c>
       <c r="K70" t="n">
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -7949,40 +7970,40 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vanguard Value ETF  [Ticker: VTV]  Qty: 6</t>
+          <t>Regeneron Pharmaceuticals Inc  [Ticker: REGN]  Qty: 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>c/o The Vanguard Group Inc, 100 Vanguard Boulevard, Malvern, PA</t>
+          <t>777 Old Saw Mill River Road, Tarrytown, NY</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94852</v>
+        <v>158782</v>
       </c>
       <c r="I71" t="n">
-        <v>102527</v>
+        <v>207178</v>
       </c>
       <c r="J71" t="n">
-        <v>102527</v>
+        <v>207178</v>
       </c>
       <c r="K71" t="n">
-        <v>1027</v>
+        <v>235</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -7991,51 +8012,51 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WisdomTree Cybersecurity UCITS ETF  [Ticker: WCBR]  Qty: 75</t>
+          <t>Rio Tinto plc - Sponsored ADR  [Ticker: RIO]  Qty: 9</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>c/o WisdomTree Issuer ICAV, Dublin</t>
+          <t>6 St James's Square, London</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>D02 T860</t>
+          <t>SW1Y 4AD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>192628</v>
+        <v>45174</v>
       </c>
       <c r="I72" t="n">
-        <v>197756</v>
+        <v>51426</v>
       </c>
       <c r="J72" t="n">
-        <v>186462</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1723</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>48914</v>
       </c>
     </row>
     <row r="73">
@@ -8049,66 +8070,716 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>RTX Corp  [Ticker: RTX]  Qty: 30</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1000 Wilson Boulevard, Arlington, VA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>22209</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>295059</v>
+      </c>
+      <c r="I73" t="n">
+        <v>418424</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L73" t="n">
+        <v>397987</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>101</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>iShares MSCI Australia UCITS ETF  [Ticker: SAUS]  Qty: 6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>c/o BlackRock Asset Management Ireland Ltd, Dublin</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>D01 W5P4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>28735</v>
+      </c>
+      <c r="I74" t="n">
+        <v>30481</v>
+      </c>
+      <c r="J74" t="n">
+        <v>30481</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Siemens AG - Registered  [Ticker: SIEd]  Qty: 20</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Werner-von-Siemens-Strasse 1, Munich</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>80333</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>327187</v>
+      </c>
+      <c r="I75" t="n">
+        <v>475224</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>447316</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Snowflake Inc  [Ticker: SNOW]  Qty: 8</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>106 East Babcock Street, Bozeman, MT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>59715</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>135016</v>
+      </c>
+      <c r="I76" t="n">
+        <v>157009</v>
+      </c>
+      <c r="J76" t="n">
+        <v>157009</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Target Corp  [Ticker: TGT]  Qty: 6</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1000 Nicollet Mall, Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>55403</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>69104</v>
+      </c>
+      <c r="I77" t="n">
+        <v>72567</v>
+      </c>
+      <c r="J77" t="n">
+        <v>52474</v>
+      </c>
+      <c r="K77" t="n">
+        <v>8298</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Target Corp  [Ticker: TGT]  Qty: 20</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1000 Nicollet Mall, Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>55403</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>160235</v>
+      </c>
+      <c r="I78" t="n">
+        <v>174914</v>
+      </c>
+      <c r="J78" t="n">
+        <v>174914</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond ETF  [Ticker: TIP]  Qty: 60</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>c/o BlackRock Fund Advisors, 400 Howard Street, San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>94105</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>544684</v>
+      </c>
+      <c r="I79" t="n">
+        <v>590019</v>
+      </c>
+      <c r="J79" t="n">
+        <v>590019</v>
+      </c>
+      <c r="K79" t="n">
+        <v>19744</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tesla Inc  [Ticker: TSLA]  Qty: 10</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1 Tesla Road, Austin, TX</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>78725</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>316639</v>
+      </c>
+      <c r="I80" t="n">
+        <v>336658</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>214358</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>212</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Co - Sponsored ADR  [Ticker: TSM]  Qty: 6</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>8 Li-Hsin Road 6, Hsinchu Science Park, Hsinchu</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>30078</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>American Depository Receipt of Listed Foreign Company</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>80895</v>
+      </c>
+      <c r="I81" t="n">
+        <v>129390</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1055</v>
+      </c>
+      <c r="L81" t="n">
+        <v>123070</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Viking Therapeutics Inc  [Ticker: VKTX]  Qty: 33</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>9920 Pacific Heights Boulevard, San Diego, CA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>92121</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>94949</v>
+      </c>
+      <c r="I82" t="n">
+        <v>100430</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>95524</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Vanguard Total World Stock ETF  [Ticker: VT]  Qty: 9</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>c/o The Vanguard Group Inc, 100 Vanguard Boulevard, Malvern, PA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19355</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>103955</v>
+      </c>
+      <c r="I83" t="n">
+        <v>113586</v>
+      </c>
+      <c r="J83" t="n">
+        <v>113586</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1270</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF  [Ticker: VTV]  Qty: 6</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>c/o The Vanguard Group Inc, 100 Vanguard Boulevard, Malvern, PA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19355</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>94852</v>
+      </c>
+      <c r="I84" t="n">
+        <v>102527</v>
+      </c>
+      <c r="J84" t="n">
+        <v>102527</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1027</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>101</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>WisdomTree Cybersecurity UCITS ETF  [Ticker: WCBR]  Qty: 75</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>c/o WisdomTree Issuer ICAV, Dublin</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>D02 T860</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>186331</v>
+      </c>
+      <c r="I85" t="n">
+        <v>197756</v>
+      </c>
+      <c r="J85" t="n">
+        <v>186461</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>Wells Fargo &amp; Company  [Ticker: WFC]  Qty: 50</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>420 Montgomery Street, San Francisco, CA</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>94104</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="H86" t="n">
         <v>339166</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I86" t="n">
         <v>416930</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J86" t="n">
         <v>416930</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K86" t="n">
         <v>2001</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L86" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="G75" t="inlineStr">
+    <row r="87"/>
+    <row r="88">
+      <c r="G88" t="inlineStr">
         <is>
           <t>TOTAL (Rs.)</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n">
-        <v>10761663</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>13150383</v>
-      </c>
-      <c r="J75" s="4" t="n">
-        <v>6044042</v>
-      </c>
-      <c r="K75" s="4" t="n">
+      <c r="H88" s="4" t="n">
+        <v>12187963</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>14654313</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>6044040</v>
+      </c>
+      <c r="K88" s="4" t="n">
         <v>97455</v>
       </c>
-      <c r="L75" s="4" t="n">
-        <v>6808569</v>
+      <c r="L88" s="4" t="n">
+        <v>6793183</v>
       </c>
     </row>
   </sheetData>
@@ -8125,7 +8796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8238,7 +8909,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -8799,7 +9470,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -8850,7 +9521,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -8861,10 +9532,10 @@
         <v>142.73</v>
       </c>
       <c r="J14" t="n">
-        <v>1927.44</v>
+        <v>194.64</v>
       </c>
       <c r="K14" t="n">
-        <v>1927.44</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8887,12 +9558,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amazon.com Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8901,27 +9572,27 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1316.34</v>
+        <v>1480.24</v>
       </c>
       <c r="J15" t="n">
-        <v>1392.12</v>
+        <v>1927.44</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1927.44</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1392.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8930,49 +9601,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASML Holding NV - NY Registered Shares</t>
+          <t>Amazon.com Inc</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4158.48</v>
+        <v>1045</v>
       </c>
       <c r="J16" t="n">
-        <v>4338.54</v>
+        <v>1392.12</v>
       </c>
       <c r="K16" t="n">
-        <v>3209.58</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>27.55</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4338.54</v>
+        <v>1392.12</v>
       </c>
     </row>
     <row r="17">
@@ -8981,49 +9652,49 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>ASML Holding NV - NY Registered Shares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2086.56</v>
+        <v>4328.71</v>
       </c>
       <c r="J17" t="n">
-        <v>2600.64</v>
+        <v>4338.54</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10.62</v>
+        <v>27.55</v>
       </c>
       <c r="M17" t="n">
-        <v>2600.64</v>
+        <v>4338.54</v>
       </c>
     </row>
     <row r="18">
@@ -9032,49 +9703,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of America Corp</t>
+          <t>ASML Holding NV - NY Registered Shares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2212.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3209.58</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3209.58</v>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2095.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2930.1</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2930.1</v>
       </c>
     </row>
     <row r="19">
@@ -9091,12 +9762,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BLBD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Blue Bird Corp</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -9105,27 +9776,27 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2317.8</v>
+        <v>1242.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2317.8</v>
+        <v>2600.64</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2060.1</v>
+        <v>2600.64</v>
       </c>
     </row>
     <row r="20">
@@ -9142,41 +9813,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Global X Robotics &amp; Artificial Intelligence ETF</t>
+          <t>Bank of America Corp</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>791.2</v>
+        <v>2095.9</v>
       </c>
       <c r="J20" t="n">
-        <v>869.52</v>
+        <v>2930.1</v>
       </c>
       <c r="K20" t="n">
-        <v>869.52</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2930.1</v>
       </c>
     </row>
     <row r="21">
@@ -9185,49 +9856,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>BLBD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>British American Tobacco plc - Sponsored ADR</t>
+          <t>Blue Bird Corp</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1198.56</v>
+        <v>2588.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1736.3</v>
+        <v>2588.8</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>76.88</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1736.3</v>
+        <v>2060.1</v>
       </c>
     </row>
     <row r="22">
@@ -9244,41 +9915,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Global X Robotics &amp; Artificial Intelligence ETF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>791.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>869.52</v>
+      </c>
+      <c r="K22" t="n">
+        <v>869.52</v>
+      </c>
+      <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2069.04</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2154.36</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>28.44</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2154.36</v>
       </c>
     </row>
     <row r="23">
@@ -9287,20 +9958,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44</v>
+        <v>234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BYDDY</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BYD Co Ltd - Unsponsored ADR</t>
+          <t>British American Tobacco plc - Sponsored ADR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -9309,27 +9980,27 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3521.86</v>
+        <v>1162.77</v>
       </c>
       <c r="J23" t="n">
-        <v>4199.58</v>
+        <v>1736.3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>46.3</v>
+        <v>76.88</v>
       </c>
       <c r="M23" t="n">
-        <v>4199.58</v>
+        <v>1736.3</v>
       </c>
     </row>
     <row r="24">
@@ -9346,12 +10017,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -9360,27 +10031,27 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1088.28</v>
+        <v>1788.57</v>
       </c>
       <c r="J24" t="n">
-        <v>3856.14</v>
+        <v>2154.36</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>30.51</v>
+        <v>28.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3856.14</v>
+        <v>2154.36</v>
       </c>
     </row>
     <row r="25">
@@ -9389,25 +10060,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CLPT</t>
+          <t>BYDDY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ClearPoint Neuro Inc</t>
+          <t>BYD Co Ltd - Unsponsored ADR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -9415,23 +10086,23 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1160.2</v>
+        <v>3521.86</v>
       </c>
       <c r="J25" t="n">
-        <v>1160.2</v>
+        <v>4199.58</v>
       </c>
       <c r="K25" t="n">
-        <v>574.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4199.58</v>
       </c>
     </row>
     <row r="26">
@@ -9448,12 +10119,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CPNG</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coupang Inc (Delaware) - Class A</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -9462,27 +10133,27 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1409.25</v>
+        <v>889.09</v>
       </c>
       <c r="J26" t="n">
-        <v>1409.25</v>
+        <v>1285.38</v>
       </c>
       <c r="K26" t="n">
-        <v>1179.5</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1285.38</v>
       </c>
     </row>
     <row r="27">
@@ -9499,12 +10170,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9513,27 +10184,27 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8094.2</v>
+        <v>1778.17</v>
       </c>
       <c r="J27" t="n">
-        <v>8094.2</v>
+        <v>2570.76</v>
       </c>
       <c r="K27" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5971.61</v>
+        <v>2570.76</v>
       </c>
     </row>
     <row r="28">
@@ -9550,12 +10221,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CLPT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>ClearPoint Neuro Inc</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9564,24 +10235,24 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1355.4</v>
+        <v>1160.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1540.6</v>
+        <v>1160.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1540.6</v>
+        <v>574.5599999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -9593,20 +10264,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>CPNG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deutsche Bank AG - Registered Shares</t>
+          <t>Coupang Inc (Delaware) - Class A</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9615,7 +10286,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -9623,13 +10294,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1208.12</v>
+        <v>1409.25</v>
       </c>
       <c r="J29" t="n">
-        <v>1272.48</v>
+        <v>1409.25</v>
       </c>
       <c r="K29" t="n">
-        <v>1272.48</v>
+        <v>1179.5</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -9652,12 +10323,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Duolingo Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9666,27 +10337,27 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2066.05</v>
+        <v>161.7</v>
       </c>
       <c r="J30" t="n">
-        <v>2066.05</v>
+        <v>161.7</v>
       </c>
       <c r="K30" t="n">
-        <v>1579.5</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>119.3</v>
       </c>
     </row>
     <row r="31">
@@ -9703,41 +10374,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WisdomTree Japan Hedged Equity Fund</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>661.74</v>
+        <v>3072.39</v>
       </c>
       <c r="J31" t="n">
-        <v>726.12</v>
+        <v>3072.39</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>726.12</v>
+        <v>2266.7</v>
       </c>
     </row>
     <row r="32">
@@ -9754,41 +10425,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EMXC</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Markets ex China ETF</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>30.0554</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>499.05</v>
+        <v>4860.1</v>
       </c>
       <c r="J32" t="n">
-        <v>576.67</v>
+        <v>4860.1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>576.67</v>
+        <v>3585.61</v>
       </c>
     </row>
     <row r="33">
@@ -9805,12 +10476,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>General Dynamics Corp</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9819,27 +10490,27 @@
         </is>
       </c>
       <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1518.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1518.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>793</v>
+      </c>
+      <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1590.52</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1898.37</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>18</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1898.37</v>
       </c>
     </row>
     <row r="34">
@@ -9856,12 +10527,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GE Aerospace / General Electric</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9870,27 +10541,27 @@
         </is>
       </c>
       <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1540.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1540.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M34" t="n">
         <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>500.37</v>
-      </c>
-      <c r="J34" t="n">
-        <v>807.28</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>807.28</v>
       </c>
     </row>
     <row r="35">
@@ -9899,29 +10570,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SPDR Gold Shares (World Gold Trust)</t>
+          <t>Deutsche Bank AG - Registered Shares</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -9929,13 +10600,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3075.89</v>
+        <v>1208.12</v>
       </c>
       <c r="J35" t="n">
-        <v>3963.1</v>
+        <v>1272.48</v>
       </c>
       <c r="K35" t="n">
-        <v>3963.1</v>
+        <v>1272.48</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9950,49 +10621,49 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HYU</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hyundai Motor Co - Reg S GDR</t>
+          <t>Duolingo Inc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Global Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>961.11</v>
+      </c>
+      <c r="J36" t="n">
+        <v>961.11</v>
+      </c>
+      <c r="K36" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1341.86</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1341.86</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1339.02</v>
       </c>
     </row>
     <row r="37">
@@ -10009,12 +10680,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Duolingo Inc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10023,24 +10694,24 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1333.8</v>
+        <v>1104.94</v>
       </c>
       <c r="J37" t="n">
-        <v>1481.05</v>
+        <v>1104.94</v>
       </c>
       <c r="K37" t="n">
-        <v>1481.05</v>
+        <v>1053</v>
       </c>
       <c r="L37" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -10060,12 +10731,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy ETF</t>
+          <t>WisdomTree Japan Hedged Equity Fund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -10074,27 +10745,27 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>710.25</v>
+        <v>609.9</v>
       </c>
       <c r="J38" t="n">
-        <v>821.5</v>
+        <v>726.12</v>
       </c>
       <c r="K38" t="n">
-        <v>821.5</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>6.41</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>726.12</v>
       </c>
     </row>
     <row r="39">
@@ -10111,12 +10782,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IGPT</t>
+          <t>EMXC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Invesco AI and Next Gen Software ETF</t>
+          <t>iShares MSCI Emerging Markets ex China ETF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10125,27 +10796,27 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1492.59</v>
+        <v>532</v>
       </c>
       <c r="J39" t="n">
-        <v>1664.68</v>
+        <v>576.67</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.55</v>
+        <v>6.4</v>
       </c>
       <c r="M39" t="n">
-        <v>1664.68</v>
+        <v>576.67</v>
       </c>
     </row>
     <row r="40">
@@ -10162,12 +10833,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Intel Corp</t>
+          <t>General Dynamics Corp</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10176,27 +10847,27 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1665.28</v>
+        <v>1590.52</v>
       </c>
       <c r="J40" t="n">
-        <v>2656.8</v>
+        <v>1898.37</v>
       </c>
       <c r="K40" t="n">
-        <v>2656.8</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1898.37</v>
       </c>
     </row>
     <row r="41">
@@ -10213,41 +10884,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IWR</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>iShares Russell Mid-Cap ETF</t>
+          <t>GE Aerospace / General Electric</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>941.65</v>
+        <v>493</v>
       </c>
       <c r="J41" t="n">
-        <v>962.7</v>
+        <v>807.28</v>
       </c>
       <c r="K41" t="n">
-        <v>962.7</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>7.16</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>807.28</v>
       </c>
     </row>
     <row r="42">
@@ -10264,41 +10935,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eli Lilly &amp; Company</t>
+          <t>SPDR Gold Shares (World Gold Trust)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4632</v>
+        <v>3075.89</v>
       </c>
       <c r="J42" t="n">
-        <v>4847.88</v>
+        <v>3963.1</v>
       </c>
       <c r="K42" t="n">
-        <v>3761.38</v>
+        <v>3963.1</v>
       </c>
       <c r="L42" t="n">
-        <v>23.25</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4847.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10307,49 +10978,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>HYU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Hyundai Motor Co - Reg S GDR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Global Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>722.3</v>
+        <v>1585.36</v>
       </c>
       <c r="J43" t="n">
-        <v>979.42</v>
+        <v>1585.36</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>6.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>979.42</v>
+        <v>1339.02</v>
       </c>
     </row>
     <row r="44">
@@ -10366,41 +11037,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MCHI</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>iShares MSCI China ETF</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1333.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1481.05</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1481.05</v>
+      </c>
+      <c r="L44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M44" t="n">
         <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1265.22</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1599.08</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1599.08</v>
       </c>
     </row>
     <row r="45">
@@ -10417,38 +11088,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc - Class A</t>
+          <t>iShares Global Clean Energy ETF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1315.52</v>
+        <v>710.25</v>
       </c>
       <c r="J45" t="n">
-        <v>1320.18</v>
+        <v>821.5</v>
       </c>
       <c r="K45" t="n">
-        <v>1320.18</v>
+        <v>821.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.05</v>
+        <v>6.41</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -10468,41 +11139,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>IGPT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Invesco AI and Next Gen Software ETF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2529</v>
+        <v>1587.97</v>
       </c>
       <c r="J46" t="n">
-        <v>3076.5</v>
+        <v>1664.68</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9.960000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3076.5</v>
+        <v>1664.68</v>
       </c>
     </row>
     <row r="47">
@@ -10511,20 +11182,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Intel Corp</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10533,7 +11204,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -10541,13 +11212,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1004.05</v>
+        <v>1665.28</v>
       </c>
       <c r="J47" t="n">
-        <v>1255.58</v>
+        <v>2656.8</v>
       </c>
       <c r="K47" t="n">
-        <v>1255.58</v>
+        <v>2656.8</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -10570,17 +11241,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>IWR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>iShares Russell Mid-Cap ETF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity Share (Company)</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10588,23 +11259,23 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2139.17</v>
+        <v>941.65</v>
       </c>
       <c r="J48" t="n">
-        <v>2797.76</v>
+        <v>962.7</v>
       </c>
       <c r="K48" t="n">
-        <v>937.6</v>
+        <v>962.7</v>
       </c>
       <c r="L48" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="M48" t="n">
         <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2797.76</v>
       </c>
     </row>
     <row r="49">
@@ -10621,41 +11292,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Eli Lilly &amp; Company</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Listed Foreign Equity / ETF</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4837</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>4847.88</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>54.96</v>
+        <v>23.25</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4847.88</v>
       </c>
     </row>
     <row r="50">
@@ -10664,20 +11335,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NOVd</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S - B Shares</t>
+          <t>Eli Lilly &amp; Company</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10686,27 +11357,27 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5558.5</v>
+        <v>2510.04</v>
       </c>
       <c r="J50" t="n">
-        <v>5558.5</v>
+        <v>3761.38</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>3761.38</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3707.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -10723,12 +11394,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NVIDIA Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10737,27 +11408,27 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1636.31</v>
+        <v>6500.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2811.59</v>
+        <v>6500.7</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2811.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10774,12 +11445,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10788,27 +11459,27 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1555.5</v>
+        <v>737.2</v>
       </c>
       <c r="J52" t="n">
-        <v>1555.5</v>
+        <v>979.42</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M52" t="n">
-        <v>980</v>
+        <v>979.42</v>
       </c>
     </row>
     <row r="53">
@@ -10825,12 +11496,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>MCHI</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust Series 1</t>
+          <t>iShares MSCI China ETF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10839,27 +11510,27 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1130.86</v>
+        <v>1527.18</v>
       </c>
       <c r="J53" t="n">
-        <v>1228.62</v>
+        <v>1599.08</v>
       </c>
       <c r="K53" t="n">
-        <v>1228.62</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2.98</v>
+        <v>14.46</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1599.08</v>
       </c>
     </row>
     <row r="54">
@@ -10868,20 +11539,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R6C0d</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Meta Platforms Inc - Class A</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10890,27 +11561,27 @@
         </is>
       </c>
       <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1315.52</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1320.18</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1320.18</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M54" t="n">
         <v>0</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1485.67</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1512.26</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1512.26</v>
       </c>
     </row>
     <row r="55">
@@ -10927,12 +11598,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rubrik Inc - Class A</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10941,27 +11612,27 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1460.11</v>
+        <v>2455</v>
       </c>
       <c r="J55" t="n">
-        <v>1460.11</v>
+        <v>3076.5</v>
       </c>
       <c r="K55" t="n">
-        <v>1300.16</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3076.5</v>
       </c>
     </row>
     <row r="56">
@@ -10970,20 +11641,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10992,24 +11663,24 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1797.19</v>
+        <v>1004.05</v>
       </c>
       <c r="J56" t="n">
-        <v>2315.61</v>
+        <v>1255.58</v>
       </c>
       <c r="K56" t="n">
-        <v>2315.61</v>
+        <v>1255.58</v>
       </c>
       <c r="L56" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -11021,49 +11692,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rio Tinto plc - Sponsored ADR</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>529.29</v>
+        <v>2226.82</v>
       </c>
       <c r="J57" t="n">
-        <v>574.78</v>
+        <v>2797.76</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>20.25</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>574.78</v>
+        <v>2797.76</v>
       </c>
     </row>
     <row r="58">
@@ -11080,12 +11751,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11094,27 +11765,27 @@
         </is>
       </c>
       <c r="G58" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1161.36</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1161.36</v>
+      </c>
+      <c r="K58" t="n">
+        <v>937.6</v>
+      </c>
+      <c r="L58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>3467.2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4676.7</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4676.7</v>
       </c>
     </row>
     <row r="59">
@@ -11123,46 +11794,46 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAUS</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>iShares MSCI Australia UCITS ETF</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity / ETF</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>337.26</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>340.68</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>340.68</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>54.96</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -11174,20 +11845,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SIEd</t>
+          <t>NOVd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Siemens AG - Registered</t>
+          <t>Novo Nordisk A/S - B Shares</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11196,18 +11867,18 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4183.69</v>
+        <v>1961.82</v>
       </c>
       <c r="J60" t="n">
-        <v>5311.54</v>
+        <v>1961.82</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -11216,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>5311.54</v>
+        <v>1308.56</v>
       </c>
     </row>
     <row r="61">
@@ -11225,20 +11896,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NOVd</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Novo Nordisk A/S - B Shares</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11247,7 +11918,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -11255,19 +11926,19 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1549.24</v>
+        <v>3596.68</v>
       </c>
       <c r="J61" t="n">
-        <v>1754.88</v>
+        <v>3596.68</v>
       </c>
       <c r="K61" t="n">
-        <v>1754.88</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2399.03</v>
       </c>
     </row>
     <row r="62">
@@ -11284,12 +11955,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>NVIDIA Corp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11298,27 +11969,27 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>811.08</v>
+        <v>424.23</v>
       </c>
       <c r="J62" t="n">
-        <v>2541.5</v>
+        <v>728.9299999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>2541.5</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>95.12</v>
+        <v>0.2</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>728.9299999999999</v>
       </c>
     </row>
     <row r="63">
@@ -11335,41 +12006,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TIP</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>iShares TIPS Bond ETF</t>
+          <t>NVIDIA Corp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6393</v>
+        <v>1212.08</v>
       </c>
       <c r="J63" t="n">
-        <v>6594.6</v>
+        <v>2082.66</v>
       </c>
       <c r="K63" t="n">
-        <v>6594.6</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>228.14</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2082.66</v>
       </c>
     </row>
     <row r="64">
@@ -11386,12 +12057,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -11400,27 +12071,27 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4038.4</v>
+        <v>1555.5</v>
       </c>
       <c r="J64" t="n">
-        <v>4038.4</v>
+        <v>1555.5</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M64" t="n">
-        <v>2465.3</v>
+        <v>980</v>
       </c>
     </row>
     <row r="65">
@@ -11429,49 +12100,49 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Co - Sponsored ADR</t>
+          <t>Invesco QQQ Trust Series 1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>American Depository Receipt of Listed Foreign Company</t>
+          <t>Exchange Traded Fund (Investment Trust)</t>
         </is>
       </c>
       <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1130.86</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1228.62</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1228.62</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M65" t="n">
         <v>0</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1184.94</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1446.18</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1446.18</v>
       </c>
     </row>
     <row r="66">
@@ -11480,20 +12151,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>234</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VKTX</t>
+          <t>R6C0d</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Viking Therapeutics Inc</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -11502,18 +12173,18 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1114.42</v>
+        <v>1502.76</v>
       </c>
       <c r="J66" t="n">
-        <v>1122.49</v>
+        <v>1512.26</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -11522,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1122.49</v>
+        <v>1512.26</v>
       </c>
     </row>
     <row r="67">
@@ -11539,21 +12210,21 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vanguard Total World Stock ETF</t>
+          <t>Rubrik Inc - Class A</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -11561,16 +12232,16 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1192.83</v>
+        <v>1460.11</v>
       </c>
       <c r="J67" t="n">
-        <v>1269.54</v>
+        <v>1460.11</v>
       </c>
       <c r="K67" t="n">
-        <v>1269.54</v>
+        <v>1300.16</v>
       </c>
       <c r="L67" t="n">
-        <v>14.34</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -11590,38 +12261,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vanguard Value ETF</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1088.38</v>
+        <v>1797.19</v>
       </c>
       <c r="J68" t="n">
-        <v>1145.94</v>
+        <v>2315.61</v>
       </c>
       <c r="K68" t="n">
-        <v>1145.94</v>
+        <v>2315.61</v>
       </c>
       <c r="L68" t="n">
-        <v>11.58</v>
+        <v>2.64</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -11633,49 +12304,49 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>WCBR</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>WisdomTree Cybersecurity UCITS ETF</t>
+          <t>Rio Tinto plc - Sponsored ADR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Exchange Traded Fund (Investment Trust)</t>
+          <t>American Depository Receipt of Listed Foreign Company</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2210.3</v>
+        <v>541</v>
       </c>
       <c r="J69" t="n">
-        <v>2210.3</v>
+        <v>574.78</v>
       </c>
       <c r="K69" t="n">
-        <v>2084.07</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>574.78</v>
       </c>
     </row>
     <row r="70">
@@ -11692,63 +12363,726 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RTX Corp</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3467.2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4676.7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M70" t="n">
+        <v>4676.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>101</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SAUS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>iShares MSCI Australia UCITS ETF</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="J71" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="K71" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>78</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SIEd</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Siemens AG - Registered</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>4183.69</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5311.54</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5311.54</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Snowflake Inc</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1549.24</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1754.88</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1754.88</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Target Corp</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>6</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>811.08</v>
+      </c>
+      <c r="J74" t="n">
+        <v>811.08</v>
+      </c>
+      <c r="K74" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Target Corp</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1882.9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1955</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond ETF</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>60</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>6393</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6594.6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6594.6</v>
+      </c>
+      <c r="L76" t="n">
+        <v>228.14</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>3762.8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3762.8</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2465.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>212</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Co - Sponsored ADR</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>American Depository Receipt of Listed Foreign Company</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>968.8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1446.18</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1446.18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VKTX</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Viking Therapeutics Inc</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Listed Foreign Equity Share (Company)</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>33</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1114.42</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1122.49</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1122.49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Vanguard Total World Stock ETF</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>9</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1192.83</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1269.54</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1269.54</v>
+      </c>
+      <c r="L80" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>6</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1088.38</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1145.94</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1145.94</v>
+      </c>
+      <c r="L81" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>101</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>WCBR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WisdomTree Cybersecurity UCITS ETF</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Exchange Traded Fund (Investment Trust)</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>75</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2210.3</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2210.3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2084.06</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>WFC</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Listed Foreign Equity Share (Company)</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G83" t="n">
         <v>50</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I83" t="n">
         <v>3891.75</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J83" t="n">
         <v>4660</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K83" t="n">
         <v>4660</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L83" t="n">
         <v>22.5</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M83" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="H71" t="inlineStr">
+    <row r="84">
+      <c r="H84" t="inlineStr">
         <is>
           <t>TOTAL (USD)</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>124872.45</v>
-      </c>
-      <c r="J71" t="n">
-        <v>146980.85</v>
-      </c>
-      <c r="K71" t="n">
-        <v>67553.8</v>
-      </c>
-      <c r="L71" t="n">
+      <c r="I84" t="n">
+        <v>143071.52</v>
+      </c>
+      <c r="J84" t="n">
+        <v>163790.18</v>
+      </c>
+      <c r="K84" t="n">
+        <v>67553.78999999999</v>
+      </c>
+      <c r="L84" t="n">
         <v>1125.58</v>
       </c>
-      <c r="M71" t="n">
-        <v>79508.33</v>
+      <c r="M84" t="n">
+        <v>79508.32000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12047,7 +13381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Interactive Brokers LLC (Clearing Broker), Advisor Client via Interactive Brokers (India) / Investment Advisor: Financial Hospital Advisory LLP</t>
+          <t xml:space="preserve">Interactive Brokers LLC (Clearing Broker), Advisor Client via Interactive Brokers (India) / Investment Advisor: </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12060,11 +13394,7 @@
           <t>06830</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>U15124027</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Owner - Sole beneficial owner</t>
@@ -12156,7 +13486,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Account: IBKR U15124027 — Ray G Stephanos (Individual, USD base, Cash).</t>
+          <t>Account: IBKR None — None (Individual, USD base, Cash).</t>
         </is>
       </c>
     </row>

--- a/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
@@ -4579,7 +4579,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xiaomi Corp - Class B  [Ticker: 1810]  Qty: 200</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>COSCO Shipping Holdings Co - H  [Ticker: 1919]  Qty: 500</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ChinaAMC Hang Seng Biotech ETF  [Ticker: 3069]  Qty: 600</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ChinaAMC Hang Seng TECH Index ETF  [Ticker: 3088]  Qty: 1000</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ChinaAMC CSI 300 Index ETF  [Ticker: 3188]  Qty: 200</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X HSCEI Covered Call ETF  [Ticker: 3416]  Qty: 1000</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Co Ltd  [Ticker: 4568.T]  Qty: 100</t>
+          <t>4568.T</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Apple Inc - Common Stock  [Ticker: AAPL]  Qty: 7</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI All Country Asia ex Japan ETF  [Ticker: AAXJ]  Qty: 8</t>
+          <t>AAXJ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Artificial Intelligence &amp; Technology ETF  [Ticker: AIQ]  Qty: 36</t>
+          <t>AIQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AIR  [Ticker: AIR]  Qty: 0</t>
+          <t>AIR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Airbus SE  [Ticker: AIRd]  Qty: 10</t>
+          <t>AIRd</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc  [Ticker: AMD]  Qty: 1.2</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc  [Ticker: AMD]  Qty: 9</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amazon.com Inc  [Ticker: AMZN]  Qty: 6</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASML Holding NV - NY Registered Shares  [Ticker: ASML]  Qty: 6</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASML Holding NV - NY Registered Shares  [Ticker: ASML]  Qty: 3</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Broadcom Inc  [Ticker: AVGO]  Qty: 9</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bank of America Corp  [Ticker: BAC]  Qty: 60</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blue Bird Corp  [Ticker: BLBD]  Qty: 60</t>
+          <t>BLBD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Global X Robotics &amp; Artificial Intelligence ETF  [Ticker: BOTZ]  Qty: 24</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>British American Tobacco plc - Sponsored ADR  [Ticker: BTI]  Qty: 33</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Blackstone Inc  [Ticker: BX]  Qty: 12</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BYD Co Ltd - Unsponsored ADR  [Ticker: BYDDY]  Qty: 42</t>
+          <t>BYDDY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Caterpillar Inc  [Ticker: CAT]  Qty: 3</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Caterpillar Inc  [Ticker: CAT]  Qty: 6</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ClearPoint Neuro Inc  [Ticker: CLPT]  Qty: 42</t>
+          <t>CLPT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Coupang Inc (Delaware) - Class A  [Ticker: CPNG]  Qty: 50</t>
+          <t>CPNG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 1</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 19</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 30.0554</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc  [Ticker: CRCL]  Qty: 10</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc  [Ticker: CSCO]  Qty: 20</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deutsche Bank AG - Registered Shares  [Ticker: DB]  Qty: 33</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Duolingo Inc  [Ticker: DUOL]  Qty: 3</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Duolingo Inc  [Ticker: DUOL]  Qty: 6</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WisdomTree Japan Hedged Equity Fund  [Ticker: DXJ]  Qty: 6</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Markets ex China ETF  [Ticker: EMXC]  Qty: 9</t>
+          <t>EMXC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>General Dynamics Corp  [Ticker: GD]  Qty: 6</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GE Aerospace / General Electric  [Ticker: GE]  Qty: 3</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SPDR Gold Shares (World Gold Trust)  [Ticker: GLD]  Qty: 10</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hyundai Motor Co - Reg S GDR  [Ticker: HYU]  Qty: 24</t>
+          <t>HYU</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>International Business Machines Corp  [Ticker: IBM]  Qty: 5</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy ETF  [Ticker: ICLN]  Qty: 50</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Invesco AI and Next Gen Software ETF  [Ticker: IGPT]  Qty: 33</t>
+          <t>IGPT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Intel Corp  [Ticker: INTC]  Qty: 72</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>iShares Russell Mid-Cap ETF  [Ticker: IWR]  Qty: 10</t>
+          <t>IWR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eli Lilly &amp; Company  [Ticker: LLY]  Qty: 6</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eli Lilly &amp; Company  [Ticker: LLY]  Qty: 3.5</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lam Research Corp  [Ticker: LRCX]  Qty: 90</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lam Research Corp  [Ticker: LRCX]  Qty: 10</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>iShares MSCI China ETF  [Ticker: MCHI]  Qty: 27</t>
+          <t>MCHI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc - Class A  [Ticker: META]  Qty: 2</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Microsoft Corp  [Ticker: MSFT]  Qty: 6</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nebius Group NV  [Ticker: NBIS]  Qty: 15</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netflix Inc  [Ticker: NFLX]  Qty: 2.4</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netflix Inc  [Ticker: NFLX]  Qty: 10</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NOV  [Ticker: NOV]  Qty: 0</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S - B Shares  [Ticker: NOVd]  Qty: 30</t>
+          <t>NOVd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S - B Shares  [Ticker: NOVd]  Qty: 55</t>
+          <t>NOVd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NVIDIA Corp  [Ticker: NVDA]  Qty: 4.2</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NVIDIA Corp  [Ticker: NVDA]  Qty: 12</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oracle Corp  [Ticker: ORCL]  Qty: 5</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust Series 1  [Ticker: QQQ]  Qty: 2</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shell plc  [Ticker: R6C0d]  Qty: 42</t>
+          <t>R6C0d</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rubrik Inc - Class A  [Ticker: RBRK]  Qty: 17</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc  [Ticker: REGN]  Qty: 3</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rio Tinto plc - Sponsored ADR  [Ticker: RIO]  Qty: 9</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RTX Corp  [Ticker: RTX]  Qty: 30</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>iShares MSCI Australia UCITS ETF  [Ticker: SAUS]  Qty: 6</t>
+          <t>SAUS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Siemens AG - Registered  [Ticker: SIEd]  Qty: 20</t>
+          <t>SIEd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Snowflake Inc  [Ticker: SNOW]  Qty: 8</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Target Corp  [Ticker: TGT]  Qty: 6</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Target Corp  [Ticker: TGT]  Qty: 20</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>iShares TIPS Bond ETF  [Ticker: TIP]  Qty: 60</t>
+          <t>TIP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tesla Inc  [Ticker: TSLA]  Qty: 10</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Co - Sponsored ADR  [Ticker: TSM]  Qty: 6</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Viking Therapeutics Inc  [Ticker: VKTX]  Qty: 33</t>
+          <t>VKTX</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Vanguard Total World Stock ETF  [Ticker: VT]  Qty: 9</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vanguard Value ETF  [Ticker: VTV]  Qty: 6</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WisdomTree Cybersecurity UCITS ETF  [Ticker: WCBR]  Qty: 75</t>
+          <t>WCBR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company  [Ticker: WFC]  Qty: 50</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">

--- a/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Ray_G_Stephanos_AY2026-27.xlsx
@@ -4168,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4188,6 +4188,11 @@
           <t>Assessee</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ray G Stephanos</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4197,7 +4202,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>None — Interactive Brokers LLC (Advisor Client; Advisor: None)</t>
+          <t>U15124027 — Interactive Brokers LLC (Advisor Client; Advisor: Financial Hospital Advisory LLP)</t>
         </is>
       </c>
     </row>
@@ -4207,6 +4212,11 @@
           <t>Customer type</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4214,6 +4224,11 @@
           <t>Base currency</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4463,7 +4478,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applicable — see sheet; opening date 06-Sep-2024 (first funding)</t>
+          <t>Applicable — see sheet; opening: 2024-09-06 (first funding / inbound transfer per IBKR)</t>
         </is>
       </c>
     </row>
@@ -4482,82 +4497,94 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A3 vs CG</t>
+          <t>A3 Col C (Name of entity)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sold lots: A3 Initial = CG Cost (INR), A3 Sale = CG Sale (INR), same Rule 115/EUR FX. Multiple buys (e.g. NOVd 21-Mar &amp; 21-Aug) appear as separate A3 rows.</t>
+          <t>Symbol only (e.g. NOVd, AAPL). Legal name / address remain in Address &amp; Nature columns.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADR country practice</t>
+          <t>A3 vs CG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
+          <t>Sold lots: A3 Initial = CG Cost (INR), A3 Sale = CG Sale (INR), same Rule 115/EUR FX. Multiple buys (e.g. NOVd 21-Mar &amp; 21-Aug) appear as separate A3 rows.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CPNG</t>
+          <t>ADR country practice</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
+          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NFLX split</t>
+          <t>CPNG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
+          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LRCX split</t>
+          <t>NFLX split</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
+          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HYU</t>
+          <t>LRCX split</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Action required</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>1) Confirm exact SBI TT Buy card rates; 2) Obtain PortfolioAnalyst for true peak NAV; 3) Map withholding to Schedule FSI/TR under DTAA.</t>
         </is>
@@ -13318,7 +13345,7 @@
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13381,7 +13408,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interactive Brokers LLC (Clearing Broker), Advisor Client via Interactive Brokers (India) / Investment Advisor: </t>
+          <t>Interactive Brokers LLC (Clearing Broker), Advisor Client via Interactive Brokers (India) / Investment Advisor: Financial Hospital Advisory LLP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13394,7 +13421,11 @@
           <t>06830</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>U15124027</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Owner - Sole beneficial owner</t>
@@ -13402,7 +13433,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-06 (first funding per IBKR deposits)</t>
+          <t>2024-09-06 (first funding / inbound transfer per IBKR)</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13517,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Account: IBKR None — None (Individual, USD base, Cash).</t>
+          <t>Account: IBKR U15124027 — Ray G Stephanos (Individual, USD base, Cash).</t>
         </is>
       </c>
     </row>
